--- a/GearSage-client/pkgGear/data_raw/daiwa_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_reels_import.xlsx
@@ -398,169 +398,1901 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:K3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>category</v>
+        <v>brand_id</v>
       </c>
       <c r="C1" t="str">
-        <v>brand</v>
+        <v>model</v>
       </c>
       <c r="D1" t="str">
-        <v>series</v>
+        <v>model_cn</v>
       </c>
       <c r="E1" t="str">
-        <v>model</v>
+        <v>model_year</v>
       </c>
       <c r="F1" t="str">
-        <v>displayName</v>
+        <v>alias</v>
       </c>
       <c r="G1" t="str">
-        <v>sourceUrl</v>
+        <v>type_tips</v>
       </c>
       <c r="H1" t="str">
+        <v>type</v>
+      </c>
+      <c r="I1" t="str">
         <v>images</v>
+      </c>
+      <c r="J1" t="str">
+        <v>created_at</v>
+      </c>
+      <c r="K1" t="str">
+        <v>updated_at</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>0R-DAIWA-1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>reel</v>
+        <v>R-DA-ソルティガ</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>Daiwa</v>
+        <v>ソルティガ</v>
       </c>
       <c r="D2" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
-        <v>シーボーグ G1800M-RJ</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>Daiwa シーボーグ G1800M-RJ</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>https://www.daiwa.com/jp/product/adbrdfh</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>https://www.daiwa.com/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG G1800M-RJ/SB G1800M-RJ_image|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/main/SEABORG_G1800M-RJ_4550133218675.jpg?rev=8e6e019cc2d247b3a2dbc3b21766cb47|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/main/SEABORG_G1800M-RJ_4550133218675_01.jpg?rev=8863a053056e4e7eb64902ce932632ae|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/main/SEABORG_G1800M-RJ_4550133218675_02.jpg?rev=c3d9b746d7434fe0807920829ad4b0ec|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/main/SEABORG_G1800M-RJ_4550133218675_03.jpg?rev=a7b4c1cfa9f34c3db5cfdf7883a252c3|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/main/SEABORG_G1800M-RJ_4550133218675_04.jpg?rev=fae72064c8c242daa538b93ba50fb956|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub26.jpg?rev=f003afc41e3d41468158a424413d13e8|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub27.png?rev=17f2e4c2a07643ea89240aa0064b03ea|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub11.jpg?rev=b421f3a587164721a9aec9224f6b0220|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub10.jpg?rev=b86a6502a8c641e090c66dcdc5f3bdc7|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub23.jpg?rev=08014e24127c48adbc304b19eb3f3c79|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub1.jpg?rev=3011d93bdaa641b8b53600f43f81e196|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub2.jpg?rev=2d066f32a9b84f4889a1b63be4813d16|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub3.jpg?rev=d7ed6ce510ed4a0ea0e35136a00c789c|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/SEABORG_G1800M-RJ_4550133218675_sub02.jpg?rev=ff6d7abb19aa4836be02476fb45f77c2|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub24.jpg?rev=dd4e7f2e13a8400fb5290171b615fbf8|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub22.png?rev=238f1ce27c614a908cde147c021b50f1|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub16.png?rev=5dd82687087e4dc3998c83a63acb68f3|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub17.png?rev=3dc6c6b83128491fba78ee7a0c9997c2|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub18.jpg?rev=ea4d984ed06849948bd0b8fa77bcc992|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/makiage.jpg?rev=d39db6b730b743a3b9205535d38c6d04|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub20.jpg?rev=daa557e384df4b29b9a1891d95a278f3|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub21_1.jpg?rev=bde824051bda4724a67d9abef5526c6a|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub6.png?rev=6dce93a396f145798af2e36f16fb6228|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub7.png?rev=69f90053c4834dfdb3252c0d84afb9eb|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub8.png?rev=43f39c8cba884293aae61355c8ddc6c4|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub4.jpg?rev=685cb34189144d879899295efa019857|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub5.jpg?rev=454f9cea75444478bba3bd9fb9076532|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/field4.jpg?rev=aaa2c44a1062474da38fe91e26d5e457|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/field3.jpg?rev=5e6bb746498c47478a209e29386348fb|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/field1.jpg?rev=d7341284858946a99ff2775558aacf4a|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/field5.jpg?rev=120200bd9f0b4f8a91e2ed1629b8ff0f|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/field7.jpg?rev=98a2d9ccba2f458689f53a7335c5729b|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/field9.jpg?rev=5d52fce9b74447f2b1a3d3de394b70ef|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/field6.jpg?rev=aa09d4e4605742688ade240891759c47|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/field8.jpg?rev=7e9fe1b7b56c4ef2a6d7a9cdc32ef38b</v>
+        <v>spinning</v>
+      </c>
+      <c r="I2" t="str">
+        <v>https://www.daiwa.com/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/banner/saltiga30000_PC_2000_640|https://www.daiwa.com/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/banner/saltiga30000_SP_1000_750|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_8000-H_4550133351426.jpg?rev=9096f5ef6aaa49f7a0918bd0e53d69c8|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_10000-P_4550133351433.jpg?rev=d6352df40a3949bfaf3b25980845e3e5|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_14000-P_4550133351457.jpg?rev=db2f67377e5b42eabc178e610527b2c8|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_18000-H_4550133351471.jpg?rev=7286843903d645f8913e3bc2b7ff8187|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_20000-H_4550133351495.jpg?rev=428625de63a445bdbcf4eb3e25fd38de|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_25000-P_4550133351501.jpg?rev=21ab7bdba7024717b5c4580d065a089d|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/tuika/25SALTIGA_30000-P_4550133420207.jpg?rev=c3a30324c63e43b49856c338ff21feab|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_8000-H_4550133351426_01.jpg?rev=3b8edff8670145a096482c76a0a39b82|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_8000-H_4550133351426_02.jpg?rev=d29ba7dd40cc455a914aa1c9f0eaa767|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_8000-H_4550133351426_03.jpg?rev=fc66efec5afd40c88b4f4198df3833a6|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_8000-H_4550133351426_05.jpg?rev=1e81ebfc28b94a8c8d4e524016a1fb22|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/POWERDRIVE-DESIGN-CONCEPT.jpg?rev=a93514e77f09478bbd66857634376310|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/POWERDRIVE-DESIGN-CONCEPT2.jpg?rev=690b5b1309ee43bcbf1b93ef0b487964|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/POWERDRIVE_ENGINE_KV.jpg?rev=bb5f39dacf8949d080a274153a3f0b44|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/OVERSIZED_POWER_DIGIGEAR_KV.jpg?rev=1b413e572fa04ff1a739b8ddb6cda2ab|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/ROLLER-POWER-OSCILLATION.jpg?rev=77d279fbc6ae4279a2e9e78917b812c8|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/POWERDRIVE_ROTOR_KV.jpg?rev=645c113a672e4065933cfc694a319b72|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/CRANK_POWER_BALL_KV.jpg?rev=2516924c2fb942748364bbfee19fd662|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/TOUGH_LINE_ROLLER_SYSTEM_KV.jpg?rev=7d6cdb23f6ab4be8b5b507e1ab24cf0f|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25SALTIGA-14000_DRD.jpg?rev=b3590b1cc80f466599262f958dcc16c4|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25SALTIGA-14000_ATD.jpg?rev=0b0e75f7d39747da80b2797e3d431f5b|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25SALTIGA_LC-ABS-SW.jpg?rev=15c37d3b63fb4772b2a07568323a332b|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25SALTIGA_stopperless.jpg?rev=03c770b1c14d4cc2a8a98b5ac7922a54|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25SALTIGA_return.jpg?rev=20b1a34d7b58490f9aa6af3169925b82|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25SALTIGA14000handlegrip.jpg?rev=fac0a764e3034e95911ad68cf2688c95|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25SALTIGASpool_graph.jpg?rev=7607e7288c5142d0b754e8a99ba6aa83|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25SALTTIGA_afterservice.jpg?rev=0c20b95fea004fdf9ba2fca7156bb71d|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25_all_bk_sample.jpg?rev=8e4cc1363bea44c8880900f05d2b88c1|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/slp-plus_black.jpg?rev=77febbc6bd634c24810408f31c37bb1f|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/banner/saltiga_SPsite_800_600.jpg?rev=cc622aecba664cff831031ef6c24bbd3|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/banner/after_25saltiga.jpg?rev=7550778bf09f42239ea8c437cee86d35|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/banner/owner_support.jpg?rev=de2ccd8608bb4121b2abc4267331865c</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0R-DAIWA-2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>reel</v>
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3" t="str">
-        <v>Daiwa</v>
+        <v>ソルティガ 4000/5000/6000</v>
       </c>
       <c r="D3" t="str">
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>シーボーグ G1200M</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>Daiwa シーボーグ G1200M</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>https://www.daiwa.com/jp/product/b6swz7y</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/b6swz7y_SEABORG_G1200M/SEABORG_G1200M_4550133430015.jpg?rev=03e79c91f8c14678b3ba9b6f8905c08d|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/b6swz7y_SEABORG_G1200M/SEABORG_G1200M_4550133430015_01.jpg?rev=2a1a4a8f1d64481693508645d4169de0|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/b6swz7y_SEABORG_G1200M/SEABORG_G1200M_4550133430015_02.jpg?rev=1c98bc9693ad4f1fa9cb0ab33d458d84|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/b6swz7y_SEABORG_G1200M/SEABORG_G1200M_4550133430015_03.jpg?rev=ccc128d24a5c4b29bbaf5774b8be6623|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/b6swz7y_SEABORG_G1200M/SEABORG_G1200M_4550133430015_04.jpg?rev=64a70e76ee0b425bbf124f3547197caa|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/b6swz7y_SEABORG_G1200M/SEABORG_G1200M_4550133430015_image_C.jpg?rev=fd9c0f0bbf8442e19e9263f227248c06|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/b6swz7y_SEABORG_G1200M/sub/sub10.jpg?rev=ad243872135241c98148f232d0c1fd23|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/b6swz7y_SEABORG_G1200M/sub/sub02.jpg?rev=45077dcfaa87493fba710f925bd2d41a|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/b6swz7y_SEABORG_G1200M/sub/sub12.jpg?rev=1de02d1f3e1246fe9b49979887fbf5d7|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/b6swz7y_SEABORG_G1200M/sub/sub05.jpg?rev=0a7c9cb552df4d0b82deb8cb7783d4dc|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/b6swz7y_SEABORG_G1200M/sub/sub03.jpg?rev=c3ba5210334c4a4b8c43e143d6d21df0|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/b6swz7y_SEABORG_G1200M/sub/sub04.jpg?rev=7af72a5644564db1b29659edcf23d835|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/b6swz7y_SEABORG_G1200M/sub/sub08.jpg?rev=141a33b0239345d6a7175f71e3c8afbf|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/b6swz7y_SEABORG_G1200M/sub/sub06.jpg?rev=4e305ca531b745b0bda4f9fb4ff9ca43|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/b6swz7y_SEABORG_G1200M/sub/sub13.jpg?rev=0b8b7e515e7b4a9384fd0f67131e837b|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/b6swz7y_SEABORG_G1200M/sub/sub09.jpg?rev=4b23d18ca9ad4a719975569953a17047|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/adbrdfh_SEABORG-G1800M-RJ/sub/sub20.jpg?rev=daa557e384df4b29b9a1891d95a278f3|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/fmpdwnh_SEABORG_G800MJ/sub/sub09.jpg?rev=75fde152562c4c7680adf4cc7a7e6373|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/fmpdwnh_SEABORG_G800MJ/sub/sub11.jpg?rev=b9d4acdbb6a44f2d84fd78a2608efe03|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/fmpdwnh_SEABORG_G800MJ/sub/sub12.jpg?rev=7a9a78c9d1584789a50943ff9a4ace46|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/fmpdwnh_SEABORG_G800MJ/sub/sub10.jpg?rev=ded7fa3ebe35480ea9041a74c1321c58|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/masterimage/dendo_app_01.jpg?rev=b636b65700b4496e971253a3fd3eb94b|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/masterimage/dendo_app_02.jpg?rev=d60281d1c7f0458cbc24847016a5e1dd</v>
+        <v>spinning</v>
+      </c>
+      <c r="I3" t="str">
+        <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_4000-H_4550133224027.jpg?rev=013e369067854758905a9c780a910b12|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_4000-XH_4550133224034.jpg?rev=bf21bc37892c46749a9843f0f1100de4|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_5000-H_4550133224041.jpg?rev=7d4a7caeaffb48529d00f62289da66b5|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_5000-XH_4550133224058.jpg?rev=050eb809c88b414abf78a0869427e305|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_6000-H_4550133224065.jpg?rev=e6cb0d62b23d4443ba4d4e5ecac482f2|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_6000-XH_4550133224072.jpg?rev=99b1aa4f4cc2431cba416022f8e7ff4c|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_6000-H_4550133224065_01.jpg?rev=b33f8a464a62420a904e324bbf3d338c|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_6000-H_4550133224065_02.jpg?rev=c637a79d7eb149888fd712e215237c73|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_6000-H_4550133224065_03.jpg?rev=b1db50336e1a4f3a9d06536f6048a563|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_6000-H_4550133224065_04.jpg?rev=437c5bafe79f4cd990985487a7b4f3ca|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/sub1.jpg?rev=0cca3a5aec4e4f0d8890f39297aad975|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/sub2.jpg?rev=8576e49e97594525ae720c2fa9896456|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/sub3.jpg?rev=1a691474d20f4eeaa90fab80f88118c1|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/sub4.jpg?rev=9688b93003734f3386d0966972ae652a|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/sub5.jpg?rev=d2f08a0e7fae4179b8f9c6b42fca6236|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/sub6.jpg?rev=5c3276285b584953be76b203ac468426|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/sub7.jpg?rev=96235172cec84d95a6f00943fc67f55e|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/25SALTTIGA_afterservice.jpg?rev=3cf4185188044e509c02df127913e2f6|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/slp-plus_black.jpg?rev=8288b1e3b6654ab4a842d56ddc4b09eb|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/SALTIGA4000_5000_6000_SPbanner.jpg?rev=3c03a1a69a7a42f7a12f85253af582f1|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/after_23saltiga4000_5000_6000.jpg?rev=21f64ba55f434d92aebdc178239fc582|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/OWNRE-SUPPORT_1.jpg?rev=b3993ae628b24b27bae1ba4316a08d21|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/masterimage/slp_works_seihinkensaku.jpg?rev=6105318184d649aab06cda9b4c6fd465</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:T29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>master_id</v>
+        <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>sku</v>
+        <v>reel_id</v>
       </c>
       <c r="C1" t="str">
-        <v>name</v>
+        <v>SKU</v>
       </c>
       <c r="D1" t="str">
-        <v>gear_ratio</v>
+        <v>GEAR RATIO</v>
       </c>
       <c r="E1" t="str">
-        <v>weight_g</v>
+        <v>DRAG</v>
       </c>
       <c r="F1" t="str">
-        <v>max_drag_kg</v>
+        <v>MAX DRAG</v>
       </c>
       <c r="G1" t="str">
-        <v>line_capacity_pe</v>
+        <v>WEIGHT</v>
+      </c>
+      <c r="H1" t="str">
+        <v>spool_diameter_per_turn_mm</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Nylon_no_m</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Nylon_lb_m</v>
+      </c>
+      <c r="K1" t="str">
+        <v>fluorocarbon_no_m</v>
+      </c>
+      <c r="L1" t="str">
+        <v>fluorocarbon_lb_m</v>
+      </c>
+      <c r="M1" t="str">
+        <v>pe_no_m</v>
+      </c>
+      <c r="N1" t="str">
+        <v>cm_per_turn</v>
+      </c>
+      <c r="O1" t="str">
+        <v>handle_length_mm</v>
+      </c>
+      <c r="P1" t="str">
+        <v>bearing_count_roller</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>market_reference_price</v>
+      </c>
+      <c r="R1" t="str">
+        <v>product_code</v>
+      </c>
+      <c r="S1" t="str">
+        <v>created_at</v>
+      </c>
+      <c r="T1" t="str">
+        <v>updated_at</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>0R-DAIWA-1</v>
+        <v/>
       </c>
       <c r="B2" t="str">
-        <v>*</v>
+        <v>R-DA-ソルティガ</v>
       </c>
       <c r="C2" t="str">
-        <v>3510</v>
+        <v>25SALTIGA 8000-P</v>
       </c>
       <c r="D2" t="str">
-        <v>14-1000/16-900</v>
-      </c>
-      <c r="E2">
-        <v>64</v>
+        <v>4.8</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>1132(1254)【1463】</v>
-      </c>
-      <c r="G2" t="str">
-        <v>85</v>
+        <v>25</v>
+      </c>
+      <c r="G2">
+        <v>670</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v>3-460_4-300</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v>80</v>
+      </c>
+      <c r="P2" t="str">
+        <v>14(14/1)</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>155,000</v>
+      </c>
+      <c r="R2" t="str">
+        <v>4550133351419</v>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0R-DAIWA-2</v>
+        <v/>
       </c>
       <c r="B3" t="str">
-        <v>*</v>
+        <v>R-DA-ソルティガ</v>
       </c>
       <c r="C3" t="str">
-        <v>2000</v>
+        <v>25SALTIGA 8000-H</v>
       </c>
       <c r="D3" t="str">
-        <v>12-800、16-550</v>
-      </c>
-      <c r="E3">
-        <v>63</v>
+        <v>5.6</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>622(689)【804】</v>
-      </c>
-      <c r="G3" t="str">
+        <v>25</v>
+      </c>
+      <c r="G3">
+        <v>680</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v>3-460_4-300</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v>80</v>
+      </c>
+      <c r="P3" t="str">
+        <v>14(14/1)</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>155,000</v>
+      </c>
+      <c r="R3" t="str">
+        <v>4550133351426</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <v>R-DA-ソルティガ</v>
+      </c>
+      <c r="C4" t="str">
+        <v>25SALTIGA 10000-P</v>
+      </c>
+      <c r="D4" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>25</v>
+      </c>
+      <c r="G4">
+        <v>675</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v>4-380_5-300</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
         <v>85</v>
+      </c>
+      <c r="P4" t="str">
+        <v>14(14/1)</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>155,000</v>
+      </c>
+      <c r="R4" t="str">
+        <v>4550133351433</v>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v>R-DA-ソルティガ</v>
+      </c>
+      <c r="C5" t="str">
+        <v>25SALTIGA 10000-H</v>
+      </c>
+      <c r="D5" t="str">
+        <v>5.6</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>685</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v>4-380_5-300</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v>85</v>
+      </c>
+      <c r="P5" t="str">
+        <v>14(14/1)</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>155,000</v>
+      </c>
+      <c r="R5" t="str">
+        <v>4550133351440</v>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
+        <v>R-DA-ソルティガ</v>
+      </c>
+      <c r="C6" t="str">
+        <v>25SALTIGA 14000-P</v>
+      </c>
+      <c r="D6" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>25</v>
+      </c>
+      <c r="G6">
+        <v>690</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v>5-340_6-300</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v>85</v>
+      </c>
+      <c r="P6" t="str">
+        <v>14(14/1)</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>155,000</v>
+      </c>
+      <c r="R6" t="str">
+        <v>4550133351457</v>
+      </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
+      <c r="T6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v>R-DA-ソルティガ</v>
+      </c>
+      <c r="C7" t="str">
+        <v>25SALTIGA 14000-XH</v>
+      </c>
+      <c r="D7" t="str">
+        <v>6.2</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>25</v>
+      </c>
+      <c r="G7">
+        <v>690</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v>5-340_6-300</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v>85</v>
+      </c>
+      <c r="P7" t="str">
+        <v>14(14/1)</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>155,000</v>
+      </c>
+      <c r="R7" t="str">
+        <v>4550133351464</v>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v>R-DA-ソルティガ</v>
+      </c>
+      <c r="C8" t="str">
+        <v>25SALTIGA 18000-H</v>
+      </c>
+      <c r="D8" t="str">
+        <v>5.5</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>30</v>
+      </c>
+      <c r="G8">
+        <v>930</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v>6-420_8-300</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v>90</v>
+      </c>
+      <c r="P8" t="str">
+        <v>14(14/1)</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>175,000</v>
+      </c>
+      <c r="R8" t="str">
+        <v>4550133351471</v>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v>R-DA-ソルティガ</v>
+      </c>
+      <c r="C9" t="str">
+        <v>25SALTIGA 20000-P</v>
+      </c>
+      <c r="D9" t="str">
+        <v>4.4</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>30</v>
+      </c>
+      <c r="G9">
+        <v>940</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v>8-370_10-300</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v>90</v>
+      </c>
+      <c r="P9" t="str">
+        <v>14(14/1)</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>175,000</v>
+      </c>
+      <c r="R9" t="str">
+        <v>4550133351488</v>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v/>
+      </c>
+      <c r="B10" t="str">
+        <v>R-DA-ソルティガ</v>
+      </c>
+      <c r="C10" t="str">
+        <v>25SALTIGA 20000-H</v>
+      </c>
+      <c r="D10" t="str">
+        <v>5.5</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>30</v>
+      </c>
+      <c r="G10">
+        <v>940</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v>8-370_10-300</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v>90</v>
+      </c>
+      <c r="P10" t="str">
+        <v>14(14/1)</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>175,000</v>
+      </c>
+      <c r="R10" t="str">
+        <v>4550133351495</v>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v/>
+      </c>
+      <c r="B11" t="str">
+        <v>R-DA-ソルティガ</v>
+      </c>
+      <c r="C11" t="str">
+        <v>25SALTIGA 25000-P</v>
+      </c>
+      <c r="D11" t="str">
+        <v>4.4</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>30</v>
+      </c>
+      <c r="G11">
+        <v>950</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v>10-360_12-300</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v>90</v>
+      </c>
+      <c r="P11" t="str">
+        <v>14(14/1)</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>175,000</v>
+      </c>
+      <c r="R11" t="str">
+        <v>4550133351501</v>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v/>
+      </c>
+      <c r="B12" t="str">
+        <v>R-DA-ソルティガ</v>
+      </c>
+      <c r="C12" t="str">
+        <v>25SALTIGA 30000-P</v>
+      </c>
+      <c r="D12" t="str">
+        <v>4.4</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>30</v>
+      </c>
+      <c r="G12">
+        <v>1060</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v>12-400_15-300</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v>95</v>
+      </c>
+      <c r="P12" t="str">
+        <v>14(14/1)</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>200,000</v>
+      </c>
+      <c r="R12" t="str">
+        <v>4550133420207</v>
+      </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
+      <c r="T12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v/>
+      </c>
+      <c r="B13" t="str">
+        <v>R-DA-ソルティガ</v>
+      </c>
+      <c r="C13" t="str">
+        <v>25SALTIGA 30000-H</v>
+      </c>
+      <c r="D13" t="str">
+        <v>5.5</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>30</v>
+      </c>
+      <c r="G13">
+        <v>1060</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v>12-400_15-300</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v>95</v>
+      </c>
+      <c r="P13" t="str">
+        <v>14(14/1)</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>200,000</v>
+      </c>
+      <c r="R13" t="str">
+        <v>4550133420214</v>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v/>
+      </c>
+      <c r="B14" t="str">
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="C14" t="str">
+        <v>4000-H</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v/>
+      </c>
+      <c r="B15" t="str">
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="C15" t="str">
+        <v>4000-XH</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v/>
+      </c>
+      <c r="B16" t="str">
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="C16" t="str">
+        <v>5000-P</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v/>
+      </c>
+      <c r="B17" t="str">
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="C17" t="str">
+        <v>5000-H</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v/>
+      </c>
+      <c r="B18" t="str">
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="C18" t="str">
+        <v>5000-XH</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str">
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v/>
+      </c>
+      <c r="B19" t="str">
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="C19" t="str">
+        <v>6000-P</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
+        <v/>
+      </c>
+      <c r="T19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v/>
+      </c>
+      <c r="B20" t="str">
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="C20" t="str">
+        <v>6000-H</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str">
+        <v/>
+      </c>
+      <c r="T20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v/>
+      </c>
+      <c r="B21" t="str">
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="C21" t="str">
+        <v>6000-XH</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str">
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v/>
+      </c>
+      <c r="B22" t="str">
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="C22" t="str">
+        <v>23ソルティガ 4000-H</v>
+      </c>
+      <c r="D22" t="str">
+        <v>5.7</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>345</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v>2-300</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v>65</v>
+      </c>
+      <c r="P22" t="str">
+        <v>12/1</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>105,000</v>
+      </c>
+      <c r="R22" t="str">
+        <v>4550133224027</v>
+      </c>
+      <c r="S22" t="str">
+        <v/>
+      </c>
+      <c r="T22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v/>
+      </c>
+      <c r="B23" t="str">
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="C23" t="str">
+        <v>23ソルティガ 4000-XH</v>
+      </c>
+      <c r="D23" t="str">
+        <v>6.2</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>12</v>
+      </c>
+      <c r="G23">
+        <v>345</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v>2-300</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v>65</v>
+      </c>
+      <c r="P23" t="str">
+        <v>12/1</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>105,000</v>
+      </c>
+      <c r="R23" t="str">
+        <v>4550133224034</v>
+      </c>
+      <c r="S23" t="str">
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v/>
+      </c>
+      <c r="B24" t="str">
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="C24" t="str">
+        <v>23ソルティガ 5000-P</v>
+      </c>
+      <c r="D24" t="str">
+        <v>4.9</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>15</v>
+      </c>
+      <c r="G24">
+        <v>365</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v>2.5-300</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v>65</v>
+      </c>
+      <c r="P24" t="str">
+        <v>12/1</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>113,000</v>
+      </c>
+      <c r="R24" t="str">
+        <v>4550133431852</v>
+      </c>
+      <c r="S24" t="str">
+        <v/>
+      </c>
+      <c r="T24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v/>
+      </c>
+      <c r="B25" t="str">
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="C25" t="str">
+        <v>23ソルティガ 5000-H</v>
+      </c>
+      <c r="D25" t="str">
+        <v>5.7</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>15</v>
+      </c>
+      <c r="G25">
+        <v>365</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v>2.5-300</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v>65</v>
+      </c>
+      <c r="P25" t="str">
+        <v>12/1</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>113,000</v>
+      </c>
+      <c r="R25" t="str">
+        <v>4550133224041</v>
+      </c>
+      <c r="S25" t="str">
+        <v/>
+      </c>
+      <c r="T25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v/>
+      </c>
+      <c r="B26" t="str">
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="C26" t="str">
+        <v>23ソルティガ 5000-XH</v>
+      </c>
+      <c r="D26" t="str">
+        <v>6.2</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>15</v>
+      </c>
+      <c r="G26">
+        <v>365</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v>2.5-300</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v>65</v>
+      </c>
+      <c r="P26" t="str">
+        <v>12/1</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>113,000</v>
+      </c>
+      <c r="R26" t="str">
+        <v>4550133224058</v>
+      </c>
+      <c r="S26" t="str">
+        <v/>
+      </c>
+      <c r="T26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v/>
+      </c>
+      <c r="B27" t="str">
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="C27" t="str">
+        <v>23ソルティガ 6000-P</v>
+      </c>
+      <c r="D27" t="str">
+        <v>4.9</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>15</v>
+      </c>
+      <c r="G27">
+        <v>400</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v>3-300</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v>70</v>
+      </c>
+      <c r="P27" t="str">
+        <v>12/1</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>115,000</v>
+      </c>
+      <c r="R27" t="str">
+        <v>4550133431869</v>
+      </c>
+      <c r="S27" t="str">
+        <v/>
+      </c>
+      <c r="T27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v/>
+      </c>
+      <c r="B28" t="str">
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="C28" t="str">
+        <v>23ソルティガ 6000-H</v>
+      </c>
+      <c r="D28" t="str">
+        <v>5.7</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>15</v>
+      </c>
+      <c r="G28">
+        <v>400</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v>3-300</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v>70</v>
+      </c>
+      <c r="P28" t="str">
+        <v>12/1</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>115,000</v>
+      </c>
+      <c r="R28" t="str">
+        <v>4550133224065</v>
+      </c>
+      <c r="S28" t="str">
+        <v/>
+      </c>
+      <c r="T28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v/>
+      </c>
+      <c r="B29" t="str">
+        <v>R-DA-ソルティガ-4000/5000/6000</v>
+      </c>
+      <c r="C29" t="str">
+        <v>23ソルティガ 6000-XH</v>
+      </c>
+      <c r="D29" t="str">
+        <v>6.2</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>15</v>
+      </c>
+      <c r="G29">
+        <v>400</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v>3-300</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v>70</v>
+      </c>
+      <c r="P29" t="str">
+        <v>12/1</v>
+      </c>
+      <c r="Q29" t="str">
+        <v>115,000</v>
+      </c>
+      <c r="R29" t="str">
+        <v>4550133224072</v>
+      </c>
+      <c r="S29" t="str">
+        <v/>
+      </c>
+      <c r="T29" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T29"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/pkgGear/data_raw/daiwa_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_reels_import.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -437,19 +437,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>ソルティガ</v>
+        <v>EXIST</v>
       </c>
       <c r="D2" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>22</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -461,60 +461,25 @@
         <v>spinning</v>
       </c>
       <c r="I2" t="str">
-        <v>https://www.daiwa.com/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/banner/saltiga30000_PC_2000_640|https://www.daiwa.com/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/banner/saltiga30000_SP_1000_750|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_8000-H_4550133351426.jpg?rev=9096f5ef6aaa49f7a0918bd0e53d69c8|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_10000-P_4550133351433.jpg?rev=d6352df40a3949bfaf3b25980845e3e5|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_14000-P_4550133351457.jpg?rev=db2f67377e5b42eabc178e610527b2c8|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_18000-H_4550133351471.jpg?rev=7286843903d645f8913e3bc2b7ff8187|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_20000-H_4550133351495.jpg?rev=428625de63a445bdbcf4eb3e25fd38de|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_25000-P_4550133351501.jpg?rev=21ab7bdba7024717b5c4580d065a089d|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/tuika/25SALTIGA_30000-P_4550133420207.jpg?rev=c3a30324c63e43b49856c338ff21feab|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_8000-H_4550133351426_01.jpg?rev=3b8edff8670145a096482c76a0a39b82|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_8000-H_4550133351426_02.jpg?rev=d29ba7dd40cc455a914aa1c9f0eaa767|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_8000-H_4550133351426_03.jpg?rev=fc66efec5afd40c88b4f4198df3833a6|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/25SALTIGA_8000-H_4550133351426_05.jpg?rev=1e81ebfc28b94a8c8d4e524016a1fb22|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/POWERDRIVE-DESIGN-CONCEPT.jpg?rev=a93514e77f09478bbd66857634376310|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/POWERDRIVE-DESIGN-CONCEPT2.jpg?rev=690b5b1309ee43bcbf1b93ef0b487964|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/POWERDRIVE_ENGINE_KV.jpg?rev=bb5f39dacf8949d080a274153a3f0b44|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/OVERSIZED_POWER_DIGIGEAR_KV.jpg?rev=1b413e572fa04ff1a739b8ddb6cda2ab|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/ROLLER-POWER-OSCILLATION.jpg?rev=77d279fbc6ae4279a2e9e78917b812c8|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/POWERDRIVE_ROTOR_KV.jpg?rev=645c113a672e4065933cfc694a319b72|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/CRANK_POWER_BALL_KV.jpg?rev=2516924c2fb942748364bbfee19fd662|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/TOUGH_LINE_ROLLER_SYSTEM_KV.jpg?rev=7d6cdb23f6ab4be8b5b507e1ab24cf0f|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25SALTIGA-14000_DRD.jpg?rev=b3590b1cc80f466599262f958dcc16c4|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25SALTIGA-14000_ATD.jpg?rev=0b0e75f7d39747da80b2797e3d431f5b|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25SALTIGA_LC-ABS-SW.jpg?rev=15c37d3b63fb4772b2a07568323a332b|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25SALTIGA_stopperless.jpg?rev=03c770b1c14d4cc2a8a98b5ac7922a54|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25SALTIGA_return.jpg?rev=20b1a34d7b58490f9aa6af3169925b82|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25SALTIGA14000handlegrip.jpg?rev=fac0a764e3034e95911ad68cf2688c95|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25SALTIGASpool_graph.jpg?rev=7607e7288c5142d0b754e8a99ba6aa83|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25SALTTIGA_afterservice.jpg?rev=0c20b95fea004fdf9ba2fca7156bb71d|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/25_all_bk_sample.jpg?rev=8e4cc1363bea44c8880900f05d2b88c1|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/sub/slp-plus_black.jpg?rev=77febbc6bd634c24810408f31c37bb1f|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/banner/saltiga_SPsite_800_600.jpg?rev=cc622aecba664cff831031ef6c24bbd3|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/banner/after_25saltiga.jpg?rev=7550778bf09f42239ea8c437cee86d35|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/i25pggl_25SALTIGA_spining/banner/owner_support.jpg?rev=de2ccd8608bb4121b2abc4267331865c</v>
+        <v>images/daiwa_reels/EXIST_main.jpg</v>
       </c>
       <c r="J2" t="str">
         <v/>
       </c>
       <c r="K2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="str">
-        <v>ソルティガ 4000/5000/6000</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I3" t="str">
-        <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_4000-H_4550133224027.jpg?rev=013e369067854758905a9c780a910b12|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_4000-XH_4550133224034.jpg?rev=bf21bc37892c46749a9843f0f1100de4|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_5000-H_4550133224041.jpg?rev=7d4a7caeaffb48529d00f62289da66b5|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_5000-XH_4550133224058.jpg?rev=050eb809c88b414abf78a0869427e305|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_6000-H_4550133224065.jpg?rev=e6cb0d62b23d4443ba4d4e5ecac482f2|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_6000-XH_4550133224072.jpg?rev=99b1aa4f4cc2431cba416022f8e7ff4c|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_6000-H_4550133224065_01.jpg?rev=b33f8a464a62420a904e324bbf3d338c|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_6000-H_4550133224065_02.jpg?rev=c637a79d7eb149888fd712e215237c73|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_6000-H_4550133224065_03.jpg?rev=b1db50336e1a4f3a9d06536f6048a563|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/main_23SALTIGA/23SALTIGA_6000-H_4550133224065_04.jpg?rev=437c5bafe79f4cd990985487a7b4f3ca|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/sub1.jpg?rev=0cca3a5aec4e4f0d8890f39297aad975|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/sub2.jpg?rev=8576e49e97594525ae720c2fa9896456|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/sub3.jpg?rev=1a691474d20f4eeaa90fab80f88118c1|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/sub4.jpg?rev=9688b93003734f3386d0966972ae652a|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/sub5.jpg?rev=d2f08a0e7fae4179b8f9c6b42fca6236|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/sub6.jpg?rev=5c3276285b584953be76b203ac468426|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/sub7.jpg?rev=96235172cec84d95a6f00943fc67f55e|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/25SALTTIGA_afterservice.jpg?rev=3cf4185188044e509c02df127913e2f6|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/slp-plus_black.jpg?rev=8288b1e3b6654ab4a842d56ddc4b09eb|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/SALTIGA4000_5000_6000_SPbanner.jpg?rev=3c03a1a69a7a42f7a12f85253af582f1|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/after_23saltiga4000_5000_6000.jpg?rev=21f64ba55f434d92aebdc178239fc582|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/reel/001/pnelxmt_SALTIGA--4000_5000_600/sub/OWNRE-SUPPORT_1.jpg?rev=b3993ae628b24b27bae1ba4316a08d21|https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/001_product_photo/masterimage/slp_works_seihinkensaku.jpg?rev=6105318184d649aab06cda9b4c6fd465</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:T22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -583,22 +548,22 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C2" t="str">
-        <v>25SALTIGA 8000-P</v>
+        <v>LT2000S-P</v>
       </c>
       <c r="D2" t="str">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>670</v>
+        <v>155</v>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -607,7 +572,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>3-150</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -616,22 +581,22 @@
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>3-460_4-300</v>
+        <v>0.4-200</v>
       </c>
       <c r="N2" t="str">
         <v/>
       </c>
       <c r="O2" t="str">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="P2" t="str">
-        <v>14(14/1)</v>
+        <v>12/1</v>
       </c>
       <c r="Q2" t="str">
-        <v>155,000</v>
+        <v>102,000</v>
       </c>
       <c r="R2" t="str">
-        <v>4550133351419</v>
+        <v>4550133109379</v>
       </c>
       <c r="S2" t="str">
         <v/>
@@ -645,22 +610,22 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C3" t="str">
-        <v>25SALTIGA 8000-H</v>
+        <v>LT2000S-H</v>
       </c>
       <c r="D3" t="str">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>680</v>
+        <v>155</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -669,7 +634,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>3-150</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -678,22 +643,22 @@
         <v/>
       </c>
       <c r="M3" t="str">
-        <v>3-460_4-300</v>
+        <v>0.4-200</v>
       </c>
       <c r="N3" t="str">
         <v/>
       </c>
       <c r="O3" t="str">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="P3" t="str">
-        <v>14(14/1)</v>
+        <v>12/1</v>
       </c>
       <c r="Q3" t="str">
-        <v>155,000</v>
+        <v>102,000</v>
       </c>
       <c r="R3" t="str">
-        <v>4550133351426</v>
+        <v>4550133109386</v>
       </c>
       <c r="S3" t="str">
         <v/>
@@ -707,22 +672,22 @@
         <v/>
       </c>
       <c r="B4" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C4" t="str">
-        <v>25SALTIGA 10000-P</v>
+        <v>LT2500S</v>
       </c>
       <c r="D4" t="str">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>675</v>
+        <v>160</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -731,7 +696,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>4-150</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -740,22 +705,22 @@
         <v/>
       </c>
       <c r="M4" t="str">
-        <v>4-380_5-300</v>
+        <v>0.6-200</v>
       </c>
       <c r="N4" t="str">
         <v/>
       </c>
       <c r="O4" t="str">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="P4" t="str">
-        <v>14(14/1)</v>
+        <v>12/1</v>
       </c>
       <c r="Q4" t="str">
-        <v>155,000</v>
+        <v>103,000</v>
       </c>
       <c r="R4" t="str">
-        <v>4550133351433</v>
+        <v>4550133109393</v>
       </c>
       <c r="S4" t="str">
         <v/>
@@ -769,22 +734,22 @@
         <v/>
       </c>
       <c r="B5" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C5" t="str">
-        <v>25SALTIGA 10000-H</v>
+        <v>LT2500S-H</v>
       </c>
       <c r="D5" t="str">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>685</v>
+        <v>160</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -793,7 +758,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>4-150</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -802,22 +767,22 @@
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>4-380_5-300</v>
+        <v>0.6-200</v>
       </c>
       <c r="N5" t="str">
         <v/>
       </c>
       <c r="O5" t="str">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="P5" t="str">
-        <v>14(14/1)</v>
+        <v>12/1</v>
       </c>
       <c r="Q5" t="str">
-        <v>155,000</v>
+        <v>103,000</v>
       </c>
       <c r="R5" t="str">
-        <v>4550133351440</v>
+        <v>4550133109409</v>
       </c>
       <c r="S5" t="str">
         <v/>
@@ -831,22 +796,22 @@
         <v/>
       </c>
       <c r="B6" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C6" t="str">
-        <v>25SALTIGA 14000-P</v>
+        <v>LT2500S-XH</v>
       </c>
       <c r="D6" t="str">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>690</v>
+        <v>160</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -855,7 +820,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>4-150</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -864,22 +829,22 @@
         <v/>
       </c>
       <c r="M6" t="str">
-        <v>5-340_6-300</v>
+        <v>0.6-200</v>
       </c>
       <c r="N6" t="str">
         <v/>
       </c>
       <c r="O6" t="str">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="P6" t="str">
-        <v>14(14/1)</v>
+        <v>12/1</v>
       </c>
       <c r="Q6" t="str">
-        <v>155,000</v>
+        <v>103,000</v>
       </c>
       <c r="R6" t="str">
-        <v>4550133351457</v>
+        <v>4550133109423</v>
       </c>
       <c r="S6" t="str">
         <v/>
@@ -893,22 +858,22 @@
         <v/>
       </c>
       <c r="B7" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C7" t="str">
-        <v>25SALTIGA 14000-XH</v>
+        <v>LT2500S-DH</v>
       </c>
       <c r="D7" t="str">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>690</v>
+        <v>170</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -917,7 +882,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>4-150</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -926,22 +891,22 @@
         <v/>
       </c>
       <c r="M7" t="str">
-        <v>5-340_6-300</v>
+        <v>0.6-200</v>
       </c>
       <c r="N7" t="str">
         <v/>
       </c>
       <c r="O7" t="str">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="P7" t="str">
-        <v>14(14/1)</v>
+        <v>14/1</v>
       </c>
       <c r="Q7" t="str">
-        <v>155,000</v>
+        <v>106,000</v>
       </c>
       <c r="R7" t="str">
-        <v>4550133351464</v>
+        <v>4550133109416</v>
       </c>
       <c r="S7" t="str">
         <v/>
@@ -955,22 +920,22 @@
         <v/>
       </c>
       <c r="B8" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C8" t="str">
-        <v>25SALTIGA 18000-H</v>
+        <v>PC LT2500</v>
       </c>
       <c r="D8" t="str">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>930</v>
+        <v>175</v>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -979,7 +944,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>6-150</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -988,22 +953,22 @@
         <v/>
       </c>
       <c r="M8" t="str">
-        <v>6-420_8-300</v>
+        <v>0.8-200</v>
       </c>
       <c r="N8" t="str">
         <v/>
       </c>
       <c r="O8" t="str">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="P8" t="str">
-        <v>14(14/1)</v>
+        <v>12/1</v>
       </c>
       <c r="Q8" t="str">
-        <v>175,000</v>
+        <v>104,000</v>
       </c>
       <c r="R8" t="str">
-        <v>4550133351471</v>
+        <v>4550133109430</v>
       </c>
       <c r="S8" t="str">
         <v/>
@@ -1017,22 +982,22 @@
         <v/>
       </c>
       <c r="B9" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C9" t="str">
-        <v>25SALTIGA 20000-P</v>
+        <v>PC LT2500-H</v>
       </c>
       <c r="D9" t="str">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>940</v>
+        <v>175</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -1041,7 +1006,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>6-150</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -1050,22 +1015,22 @@
         <v/>
       </c>
       <c r="M9" t="str">
-        <v>8-370_10-300</v>
+        <v>0.8-200</v>
       </c>
       <c r="N9" t="str">
         <v/>
       </c>
       <c r="O9" t="str">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="P9" t="str">
-        <v>14(14/1)</v>
+        <v>12/1</v>
       </c>
       <c r="Q9" t="str">
-        <v>175,000</v>
+        <v>104,000</v>
       </c>
       <c r="R9" t="str">
-        <v>4550133351488</v>
+        <v>4550133326004</v>
       </c>
       <c r="S9" t="str">
         <v/>
@@ -1079,22 +1044,22 @@
         <v/>
       </c>
       <c r="B10" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C10" t="str">
-        <v>25SALTIGA 20000-H</v>
+        <v>LT3000S</v>
       </c>
       <c r="D10" t="str">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>940</v>
+        <v>180</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -1103,7 +1068,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>6-150</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -1112,22 +1077,22 @@
         <v/>
       </c>
       <c r="M10" t="str">
-        <v>8-370_10-300</v>
+        <v>0.8-200</v>
       </c>
       <c r="N10" t="str">
         <v/>
       </c>
       <c r="O10" t="str">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="P10" t="str">
-        <v>14(14/1)</v>
+        <v>12/1</v>
       </c>
       <c r="Q10" t="str">
-        <v>175,000</v>
+        <v>105,000</v>
       </c>
       <c r="R10" t="str">
-        <v>4550133351495</v>
+        <v>4550133109454</v>
       </c>
       <c r="S10" t="str">
         <v/>
@@ -1141,22 +1106,22 @@
         <v/>
       </c>
       <c r="B11" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C11" t="str">
-        <v>25SALTIGA 25000-P</v>
+        <v>LT3000-H</v>
       </c>
       <c r="D11" t="str">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>950</v>
+        <v>180</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -1165,7 +1130,7 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>8-150</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -1174,22 +1139,22 @@
         <v/>
       </c>
       <c r="M11" t="str">
-        <v>10-360_12-300</v>
+        <v>1-200</v>
       </c>
       <c r="N11" t="str">
         <v/>
       </c>
       <c r="O11" t="str">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="P11" t="str">
-        <v>14(14/1)</v>
+        <v>12/1</v>
       </c>
       <c r="Q11" t="str">
-        <v>175,000</v>
+        <v>105,000</v>
       </c>
       <c r="R11" t="str">
-        <v>4550133351501</v>
+        <v>4550133326011</v>
       </c>
       <c r="S11" t="str">
         <v/>
@@ -1203,22 +1168,22 @@
         <v/>
       </c>
       <c r="B12" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C12" t="str">
-        <v>25SALTIGA 30000-P</v>
+        <v>PC LT3000</v>
       </c>
       <c r="D12" t="str">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>1060</v>
+        <v>190</v>
       </c>
       <c r="H12" t="str">
         <v/>
@@ -1227,7 +1192,7 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>8-150</v>
       </c>
       <c r="K12" t="str">
         <v/>
@@ -1236,22 +1201,22 @@
         <v/>
       </c>
       <c r="M12" t="str">
-        <v>12-400_15-300</v>
+        <v>1-200</v>
       </c>
       <c r="N12" t="str">
         <v/>
       </c>
       <c r="O12" t="str">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="P12" t="str">
-        <v>14(14/1)</v>
+        <v>12/1</v>
       </c>
       <c r="Q12" t="str">
-        <v>200,000</v>
+        <v>106,000</v>
       </c>
       <c r="R12" t="str">
-        <v>4550133420207</v>
+        <v>4550133109478</v>
       </c>
       <c r="S12" t="str">
         <v/>
@@ -1265,22 +1230,22 @@
         <v/>
       </c>
       <c r="B13" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C13" t="str">
-        <v>25SALTIGA 30000-H</v>
+        <v>PC LT3000-XH</v>
       </c>
       <c r="D13" t="str">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>1060</v>
+        <v>190</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -1289,7 +1254,7 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v/>
+        <v>8-150</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -1298,22 +1263,22 @@
         <v/>
       </c>
       <c r="M13" t="str">
-        <v>12-400_15-300</v>
+        <v>1-200</v>
       </c>
       <c r="N13" t="str">
         <v/>
       </c>
       <c r="O13" t="str">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="P13" t="str">
-        <v>14(14/1)</v>
+        <v>12/1</v>
       </c>
       <c r="Q13" t="str">
-        <v>200,000</v>
+        <v>106,000</v>
       </c>
       <c r="R13" t="str">
-        <v>4550133420214</v>
+        <v>4550133109485</v>
       </c>
       <c r="S13" t="str">
         <v/>
@@ -1327,19 +1292,22 @@
         <v/>
       </c>
       <c r="B14" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C14" t="str">
-        <v>4000-H</v>
+        <v>LT4000</v>
       </c>
       <c r="D14" t="str">
-        <v/>
+        <v>5.2</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>205</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -1348,7 +1316,7 @@
         <v/>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>12-150</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -1357,22 +1325,22 @@
         <v/>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>1.5-200</v>
       </c>
       <c r="N14" t="str">
         <v/>
       </c>
       <c r="O14" t="str">
-        <v/>
+        <v>60</v>
       </c>
       <c r="P14" t="str">
-        <v/>
+        <v>12/1</v>
       </c>
       <c r="Q14" t="str">
-        <v/>
+        <v>107,000</v>
       </c>
       <c r="R14" t="str">
-        <v/>
+        <v>4550133109492</v>
       </c>
       <c r="S14" t="str">
         <v/>
@@ -1386,19 +1354,22 @@
         <v/>
       </c>
       <c r="B15" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C15" t="str">
-        <v>4000-XH</v>
+        <v>LT4000-XH</v>
       </c>
       <c r="D15" t="str">
-        <v/>
+        <v>6.2</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>205</v>
       </c>
       <c r="H15" t="str">
         <v/>
@@ -1407,7 +1378,7 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>12-150</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -1416,22 +1387,22 @@
         <v/>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>1.5-200</v>
       </c>
       <c r="N15" t="str">
         <v/>
       </c>
       <c r="O15" t="str">
-        <v/>
+        <v>60</v>
       </c>
       <c r="P15" t="str">
-        <v/>
+        <v>12/1</v>
       </c>
       <c r="Q15" t="str">
-        <v/>
+        <v>107,000</v>
       </c>
       <c r="R15" t="str">
-        <v/>
+        <v>4550133109508</v>
       </c>
       <c r="S15" t="str">
         <v/>
@@ -1445,19 +1416,22 @@
         <v/>
       </c>
       <c r="B16" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C16" t="str">
-        <v>5000-P</v>
+        <v>LT5000-C</v>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>5.2</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>220</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -1466,7 +1440,7 @@
         <v/>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>20-150</v>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -1475,22 +1449,22 @@
         <v/>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>2-300</v>
       </c>
       <c r="N16" t="str">
         <v/>
       </c>
       <c r="O16" t="str">
-        <v/>
+        <v>60</v>
       </c>
       <c r="P16" t="str">
-        <v/>
+        <v>12/1</v>
       </c>
       <c r="Q16" t="str">
-        <v/>
+        <v>110,000</v>
       </c>
       <c r="R16" t="str">
-        <v/>
+        <v>4550133109515</v>
       </c>
       <c r="S16" t="str">
         <v/>
@@ -1504,19 +1478,22 @@
         <v/>
       </c>
       <c r="B17" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C17" t="str">
-        <v>5000-H</v>
+        <v>LT5000-CXH</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>6.2</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>220</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -1525,7 +1502,7 @@
         <v/>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>20-150</v>
       </c>
       <c r="K17" t="str">
         <v/>
@@ -1534,22 +1511,22 @@
         <v/>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>2-300</v>
       </c>
       <c r="N17" t="str">
         <v/>
       </c>
       <c r="O17" t="str">
-        <v/>
+        <v>60</v>
       </c>
       <c r="P17" t="str">
-        <v/>
+        <v>12/1</v>
       </c>
       <c r="Q17" t="str">
-        <v/>
+        <v>110,000</v>
       </c>
       <c r="R17" t="str">
-        <v/>
+        <v>4550133109522</v>
       </c>
       <c r="S17" t="str">
         <v/>
@@ -1563,19 +1540,22 @@
         <v/>
       </c>
       <c r="B18" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C18" t="str">
-        <v>5000-XH</v>
+        <v>SF1000S-P</v>
       </c>
       <c r="D18" t="str">
-        <v/>
+        <v>4.6</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="G18">
+        <v>135</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -1584,7 +1564,7 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>2.5-100</v>
       </c>
       <c r="K18" t="str">
         <v/>
@@ -1593,22 +1573,22 @@
         <v/>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>0.3-200</v>
       </c>
       <c r="N18" t="str">
         <v/>
       </c>
       <c r="O18" t="str">
-        <v/>
+        <v>35</v>
       </c>
       <c r="P18" t="str">
-        <v/>
+        <v>11/1</v>
       </c>
       <c r="Q18" t="str">
-        <v/>
+        <v>102,000</v>
       </c>
       <c r="R18" t="str">
-        <v/>
+        <v>4550133173059</v>
       </c>
       <c r="S18" t="str">
         <v/>
@@ -1622,19 +1602,22 @@
         <v/>
       </c>
       <c r="B19" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C19" t="str">
-        <v>6000-P</v>
+        <v>SF2000SS-P</v>
       </c>
       <c r="D19" t="str">
-        <v/>
+        <v>4.6</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="G19">
+        <v>135</v>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -1643,7 +1626,7 @@
         <v/>
       </c>
       <c r="J19" t="str">
-        <v/>
+        <v>2.5-100</v>
       </c>
       <c r="K19" t="str">
         <v/>
@@ -1652,22 +1635,22 @@
         <v/>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>0.3-200</v>
       </c>
       <c r="N19" t="str">
         <v/>
       </c>
       <c r="O19" t="str">
-        <v/>
+        <v>40</v>
       </c>
       <c r="P19" t="str">
-        <v/>
+        <v>11/1</v>
       </c>
       <c r="Q19" t="str">
-        <v/>
+        <v>102,000</v>
       </c>
       <c r="R19" t="str">
-        <v/>
+        <v>4550133173066</v>
       </c>
       <c r="S19" t="str">
         <v/>
@@ -1681,19 +1664,22 @@
         <v/>
       </c>
       <c r="B20" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C20" t="str">
-        <v>6000-H</v>
+        <v>SF2000SS-H</v>
       </c>
       <c r="D20" t="str">
-        <v/>
+        <v>5.7</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="G20">
+        <v>135</v>
       </c>
       <c r="H20" t="str">
         <v/>
@@ -1702,7 +1688,7 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v/>
+        <v>2.5-100</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -1711,22 +1697,22 @@
         <v/>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>0.3-200</v>
       </c>
       <c r="N20" t="str">
         <v/>
       </c>
       <c r="O20" t="str">
-        <v/>
+        <v>45</v>
       </c>
       <c r="P20" t="str">
-        <v/>
+        <v>11/1</v>
       </c>
       <c r="Q20" t="str">
-        <v/>
+        <v>102,000</v>
       </c>
       <c r="R20" t="str">
-        <v/>
+        <v>4550133173073</v>
       </c>
       <c r="S20" t="str">
         <v/>
@@ -1740,19 +1726,22 @@
         <v/>
       </c>
       <c r="B21" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C21" t="str">
-        <v>6000-XH</v>
+        <v>SF2500SS</v>
       </c>
       <c r="D21" t="str">
-        <v/>
+        <v>5.0</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>140</v>
       </c>
       <c r="H21" t="str">
         <v/>
@@ -1761,7 +1750,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v/>
+        <v>3-150</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -1770,22 +1759,22 @@
         <v/>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>0.4-200</v>
       </c>
       <c r="N21" t="str">
         <v/>
       </c>
       <c r="O21" t="str">
-        <v/>
+        <v>45</v>
       </c>
       <c r="P21" t="str">
-        <v/>
+        <v>11/1</v>
       </c>
       <c r="Q21" t="str">
-        <v/>
+        <v>103,000</v>
       </c>
       <c r="R21" t="str">
-        <v/>
+        <v>4550133173080</v>
       </c>
       <c r="S21" t="str">
         <v/>
@@ -1799,10 +1788,10 @@
         <v/>
       </c>
       <c r="B22" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-EXIST</v>
       </c>
       <c r="C22" t="str">
-        <v>23ソルティガ 4000-H</v>
+        <v>SF2500SS-H</v>
       </c>
       <c r="D22" t="str">
         <v>5.7</v>
@@ -1811,10 +1800,10 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G22">
-        <v>345</v>
+        <v>140</v>
       </c>
       <c r="H22" t="str">
         <v/>
@@ -1823,7 +1812,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v/>
+        <v>3-150</v>
       </c>
       <c r="K22" t="str">
         <v/>
@@ -1832,467 +1821,33 @@
         <v/>
       </c>
       <c r="M22" t="str">
-        <v>2-300</v>
+        <v>0.4-200</v>
       </c>
       <c r="N22" t="str">
         <v/>
       </c>
       <c r="O22" t="str">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="P22" t="str">
-        <v>12/1</v>
+        <v>11/1</v>
       </c>
       <c r="Q22" t="str">
-        <v>105,000</v>
+        <v>103,000</v>
       </c>
       <c r="R22" t="str">
-        <v>4550133224027</v>
+        <v>4550133173097</v>
       </c>
       <c r="S22" t="str">
         <v/>
       </c>
       <c r="T22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v/>
-      </c>
-      <c r="B23" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
-      </c>
-      <c r="C23" t="str">
-        <v>23ソルティガ 4000-XH</v>
-      </c>
-      <c r="D23" t="str">
-        <v>6.2</v>
-      </c>
-      <c r="E23" t="str">
-        <v/>
-      </c>
-      <c r="F23" t="str">
-        <v>12</v>
-      </c>
-      <c r="G23">
-        <v>345</v>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="J23" t="str">
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <v>2-300</v>
-      </c>
-      <c r="N23" t="str">
-        <v/>
-      </c>
-      <c r="O23" t="str">
-        <v>65</v>
-      </c>
-      <c r="P23" t="str">
-        <v>12/1</v>
-      </c>
-      <c r="Q23" t="str">
-        <v>105,000</v>
-      </c>
-      <c r="R23" t="str">
-        <v>4550133224034</v>
-      </c>
-      <c r="S23" t="str">
-        <v/>
-      </c>
-      <c r="T23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v/>
-      </c>
-      <c r="B24" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
-      </c>
-      <c r="C24" t="str">
-        <v>23ソルティガ 5000-P</v>
-      </c>
-      <c r="D24" t="str">
-        <v>4.9</v>
-      </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
-      <c r="F24" t="str">
-        <v>15</v>
-      </c>
-      <c r="G24">
-        <v>365</v>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <v>2.5-300</v>
-      </c>
-      <c r="N24" t="str">
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <v>65</v>
-      </c>
-      <c r="P24" t="str">
-        <v>12/1</v>
-      </c>
-      <c r="Q24" t="str">
-        <v>113,000</v>
-      </c>
-      <c r="R24" t="str">
-        <v>4550133431852</v>
-      </c>
-      <c r="S24" t="str">
-        <v/>
-      </c>
-      <c r="T24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v/>
-      </c>
-      <c r="B25" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
-      </c>
-      <c r="C25" t="str">
-        <v>23ソルティガ 5000-H</v>
-      </c>
-      <c r="D25" t="str">
-        <v>5.7</v>
-      </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
-      <c r="F25" t="str">
-        <v>15</v>
-      </c>
-      <c r="G25">
-        <v>365</v>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
-      <c r="M25" t="str">
-        <v>2.5-300</v>
-      </c>
-      <c r="N25" t="str">
-        <v/>
-      </c>
-      <c r="O25" t="str">
-        <v>65</v>
-      </c>
-      <c r="P25" t="str">
-        <v>12/1</v>
-      </c>
-      <c r="Q25" t="str">
-        <v>113,000</v>
-      </c>
-      <c r="R25" t="str">
-        <v>4550133224041</v>
-      </c>
-      <c r="S25" t="str">
-        <v/>
-      </c>
-      <c r="T25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v/>
-      </c>
-      <c r="B26" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
-      </c>
-      <c r="C26" t="str">
-        <v>23ソルティガ 5000-XH</v>
-      </c>
-      <c r="D26" t="str">
-        <v>6.2</v>
-      </c>
-      <c r="E26" t="str">
-        <v/>
-      </c>
-      <c r="F26" t="str">
-        <v>15</v>
-      </c>
-      <c r="G26">
-        <v>365</v>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
-      <c r="M26" t="str">
-        <v>2.5-300</v>
-      </c>
-      <c r="N26" t="str">
-        <v/>
-      </c>
-      <c r="O26" t="str">
-        <v>65</v>
-      </c>
-      <c r="P26" t="str">
-        <v>12/1</v>
-      </c>
-      <c r="Q26" t="str">
-        <v>113,000</v>
-      </c>
-      <c r="R26" t="str">
-        <v>4550133224058</v>
-      </c>
-      <c r="S26" t="str">
-        <v/>
-      </c>
-      <c r="T26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v/>
-      </c>
-      <c r="B27" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
-      </c>
-      <c r="C27" t="str">
-        <v>23ソルティガ 6000-P</v>
-      </c>
-      <c r="D27" t="str">
-        <v>4.9</v>
-      </c>
-      <c r="E27" t="str">
-        <v/>
-      </c>
-      <c r="F27" t="str">
-        <v>15</v>
-      </c>
-      <c r="G27">
-        <v>400</v>
-      </c>
-      <c r="H27" t="str">
-        <v/>
-      </c>
-      <c r="I27" t="str">
-        <v/>
-      </c>
-      <c r="J27" t="str">
-        <v/>
-      </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27" t="str">
-        <v/>
-      </c>
-      <c r="M27" t="str">
-        <v>3-300</v>
-      </c>
-      <c r="N27" t="str">
-        <v/>
-      </c>
-      <c r="O27" t="str">
-        <v>70</v>
-      </c>
-      <c r="P27" t="str">
-        <v>12/1</v>
-      </c>
-      <c r="Q27" t="str">
-        <v>115,000</v>
-      </c>
-      <c r="R27" t="str">
-        <v>4550133431869</v>
-      </c>
-      <c r="S27" t="str">
-        <v/>
-      </c>
-      <c r="T27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v/>
-      </c>
-      <c r="B28" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
-      </c>
-      <c r="C28" t="str">
-        <v>23ソルティガ 6000-H</v>
-      </c>
-      <c r="D28" t="str">
-        <v>5.7</v>
-      </c>
-      <c r="E28" t="str">
-        <v/>
-      </c>
-      <c r="F28" t="str">
-        <v>15</v>
-      </c>
-      <c r="G28">
-        <v>400</v>
-      </c>
-      <c r="H28" t="str">
-        <v/>
-      </c>
-      <c r="I28" t="str">
-        <v/>
-      </c>
-      <c r="J28" t="str">
-        <v/>
-      </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28" t="str">
-        <v/>
-      </c>
-      <c r="M28" t="str">
-        <v>3-300</v>
-      </c>
-      <c r="N28" t="str">
-        <v/>
-      </c>
-      <c r="O28" t="str">
-        <v>70</v>
-      </c>
-      <c r="P28" t="str">
-        <v>12/1</v>
-      </c>
-      <c r="Q28" t="str">
-        <v>115,000</v>
-      </c>
-      <c r="R28" t="str">
-        <v>4550133224065</v>
-      </c>
-      <c r="S28" t="str">
-        <v/>
-      </c>
-      <c r="T28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v/>
-      </c>
-      <c r="B29" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
-      </c>
-      <c r="C29" t="str">
-        <v>23ソルティガ 6000-XH</v>
-      </c>
-      <c r="D29" t="str">
-        <v>6.2</v>
-      </c>
-      <c r="E29" t="str">
-        <v/>
-      </c>
-      <c r="F29" t="str">
-        <v>15</v>
-      </c>
-      <c r="G29">
-        <v>400</v>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <v/>
-      </c>
-      <c r="J29" t="str">
-        <v/>
-      </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
-      <c r="L29" t="str">
-        <v/>
-      </c>
-      <c r="M29" t="str">
-        <v>3-300</v>
-      </c>
-      <c r="N29" t="str">
-        <v/>
-      </c>
-      <c r="O29" t="str">
-        <v>70</v>
-      </c>
-      <c r="P29" t="str">
-        <v>12/1</v>
-      </c>
-      <c r="Q29" t="str">
-        <v>115,000</v>
-      </c>
-      <c r="R29" t="str">
-        <v>4550133224072</v>
-      </c>
-      <c r="S29" t="str">
-        <v/>
-      </c>
-      <c r="T29" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/pkgGear/data_raw/daiwa_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_reels_import.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,7 +449,7 @@
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-ソルティガ-2025</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -492,21 +492,21 @@
         <v>在售</v>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>2026-04-03 18:54:42</v>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>2026-04-03 18:54:42</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="str">
-        <v>ソルティガ 4000/5000/6000</v>
+        <v>ソルティガ</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -541,15 +541,15 @@
         <v>在售</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>2026-04-03 18:54:42</v>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>2026-04-03 18:54:42</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -591,22 +591,120 @@
         <v>在售</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>2026-04-03 18:54:42</v>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>2026-04-03 18:54:42</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>R-DA-セルテート-SW-2026</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="str">
+        <v>セルテート SW</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v>2026</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="J5" t="str">
+        <v>images/daiwa_reels/セルテート_SW_8000___10000___14000___18000___20000_main.jpg</v>
+      </c>
+      <c r="K5" t="str" xml:space="preserve">
+        <v xml:space="preserve">MONOCOQUE BODY
+                                                                    強靭・耐久テクノロジー、モノコックボディ。従来スピニングリールは、ボディとボディカバーでドライブギアの両端を支持し、それを数箇所のスクリューで固定する方式が一般的でした。この構造から、更なる精度と剛性の向上を目指し、ボディカバーを廃し、ボディに直接高精度のプレートをねじ込むことで固定したのがモノコックボディ。これによりギアの支持精度が高まり、また剛性･気密性も向上しました。更には、従来スクリューに取られていたスペースを活用し、ドライブギアのサイズを極限まで拡大することにも成功。モノコックボディとは、MONO（ひとつの） - COQUE（殻）という意味。一枚貝の殻がそうであるような強靭さを象徴する、まったく新しい形状はリール構造の常識を打ち破ります。 | POWERDRIVE DESIGN
+                                                                    パワードライブデザインは、世界中の大型魚と安心して渡り合える高い信頼性を追求した次世代大型スピニングリールの設計思想。このパワードライブデザインは、高効率で力強い巻き上げ力を実現するボディユニット[パワードライブエンジン]と、合理的な球体形状で高剛性と低イナーシャの両立を実現したローターユニット[パワードライブローター]の２つのテクノロジーユニットからなる。ボディユニットの[パワードライブエンジン]は、[オーバーサイズドパワーデジギア]と[ローラーパワーオシレーション]の２つのテクノロジーによって構成される。[オーバーサイズドパワーデジギア]は大口径化・肉厚化と、最適化された歯面形状により、ギアの駆動効率を大幅にアップ。[ローラーパワーオシレーション]はオシレート機構にベアリング方式を採用することで、摩擦抵抗を大幅に低減し、初動レスポンスの向上と、軽い巻き上げを実現した。一方、フロントユニットは、[クランクパワーベール]と[タフラインローラーシステム]の２つのテクノロジーを搭載した[パワードライブローター]によって構成される。[クランクパワーベール]は、ベールの開閉力を強化するとともに、クランク形状を採用することで、ラインローラーへの確実な糸送りを実現。[タフラインローラーシステム]は、ラインローラーの支持構造や形状を見直すことで、耐久性やトラブルレス性を向上させた。これらのテクノロジーの相乗効果により、大型魚をターゲットとしたキャスティングゲームやジギングゲームにおいて、剛性・パワー・耐久性を高次元で実現する。獲るための“強さ”を、ビッグゲームを愛する、すべてのアングラーに。 | ROLLER POWER OSCILLATION
+                                                                    高負荷が絶え間なく続く大型魚とのファイトでは、巻き上げで生じるオシレート部の摩擦抵抗がパワーの伝達ロスに繋がる。その摩擦を極限まで減らすべく、摺動部分は従来のピラー式から2ベアリング式オシレートに変更。これによりオシレート効率は約30%向上し、高負荷時でもスムーズな初動レスポンスと、軽くてパワフルな巻き上げを実現した。※当社比較テストによる。</v>
+      </c>
+      <c r="L5" t="str">
+        <v>¥93,100 - ¥104,500</v>
+      </c>
+      <c r="M5" t="str">
+        <v>在售</v>
+      </c>
+      <c r="N5" t="str">
+        <v>2026-04-03 18:54:42</v>
+      </c>
+      <c r="O5" t="str">
+        <v>2026-04-03 18:54:42</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>R-DA-トーナメントサーフ-45-2019</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="str">
+        <v>トーナメントサーフ 45</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v>2019</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str" xml:space="preserve">
+        <v xml:space="preserve">さらに先に。「TOURNAMENT」。TOURNAMENTは、トーナメンターを勝利に導くために、先進・先鋭のテクノロジーを搭載し、進化し続ける。「さらに遠くへ」「さらに感度よく」。激化するトーナメントシーンを勝ち残るための、トーナメンターの要求は厳しい。目指すのは、釣りの技術に革新をもたらし、アングラーの満足感へと繋がるプロダクト。最先端の技術をいち早く採り入れ、トーナメントの新しい基準を築き上げていく。TOURNAMENTの勝利への探求が終わることはなく、常にトーナメンターとともにある。 | すべては勝つために。現在のキストーナメントシーンにおいて求められる性能とは何か。リール形状そのものから見直し、まさにゼロから新たなTOURNAMENTを創り上げた。45mmストロークだからこそ実現可能な中近距離から遠距離までカバーできる対応力。遠投域からトルクフル&amp;スムーズな巻き上げ性能。起伏変化をキャスターへ伝えるブレのない回転性能。過酷なキストーナメントシーンで、初期性能を維持する高耐久性能。これらは単にスペックの向上ではない、とことん実釣にこだわり、キャスターの武器になるための進化だ。テーパー角別専用設計「LCスプール」搭載により、理想の放出性能を実現。強さと軽さをもたらすZAIONハウジング、心臓部には高負荷でも屈しないアルミマシンカットタフデジギアで武装し、さらなる高耐久性を実現。ワンピースエアベールによる至極の回転性能は、より快適に、より精悍に。シリーズ最速となるギア比「4.9」の登場により、キストーナメントシーンに衝撃を与える。「DAIWA TECHNOLOGY」のすべてを惜しむことなく投入し、飛距離、回転性能を追い求めた答えが、今ここにある。※ハンドルノブS交換可※ソルト対応 | TOUGH DIGIGEAR
+                                                                    過酷な環境に耐え抜くにはリールを支える強靭な心臓部が必要です。滑らかな回転がより長く続く「タフデジギア」。</v>
+      </c>
+      <c r="L6" t="str">
+        <v>¥98,000</v>
+      </c>
+      <c r="M6" t="str">
+        <v>在售</v>
+      </c>
+      <c r="N6" t="str">
+        <v>2026-04-03 18:54:42</v>
+      </c>
+      <c r="O6" t="str">
+        <v>2026-04-03 18:54:42</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S50"/>
+  <dimension ref="A1:S62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -672,7 +770,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-ソルティガ-2025</v>
       </c>
       <c r="C2" t="str">
         <v>SALTIGA 8000-P</v>
@@ -720,10 +818,10 @@
         <v>标准杯</v>
       </c>
       <c r="R2" t="str">
-        <v>低齿比 (P/PG)</v>
+        <v>低速比 (P/PG)</v>
       </c>
       <c r="S2" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -731,7 +829,7 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-ソルティガ-2025</v>
       </c>
       <c r="C3" t="str">
         <v>SALTIGA 8000-H</v>
@@ -779,10 +877,10 @@
         <v>标准杯</v>
       </c>
       <c r="R3" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S3" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -790,7 +888,7 @@
         <v/>
       </c>
       <c r="B4" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-ソルティガ-2025</v>
       </c>
       <c r="C4" t="str">
         <v>SALTIGA 10000-P</v>
@@ -838,10 +936,10 @@
         <v>标准杯</v>
       </c>
       <c r="R4" t="str">
-        <v>低齿比 (P/PG)</v>
+        <v>低速比 (P/PG)</v>
       </c>
       <c r="S4" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -849,7 +947,7 @@
         <v/>
       </c>
       <c r="B5" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-ソルティガ-2025</v>
       </c>
       <c r="C5" t="str">
         <v>SALTIGA 10000-H</v>
@@ -897,10 +995,10 @@
         <v>标准杯</v>
       </c>
       <c r="R5" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S5" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -908,7 +1006,7 @@
         <v/>
       </c>
       <c r="B6" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-ソルティガ-2025</v>
       </c>
       <c r="C6" t="str">
         <v>SALTIGA 14000-P</v>
@@ -956,10 +1054,10 @@
         <v>标准杯</v>
       </c>
       <c r="R6" t="str">
-        <v>低齿比 (P/PG)</v>
+        <v>低速比 (P/PG)</v>
       </c>
       <c r="S6" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -967,7 +1065,7 @@
         <v/>
       </c>
       <c r="B7" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-ソルティガ-2025</v>
       </c>
       <c r="C7" t="str">
         <v>SALTIGA 14000-XH</v>
@@ -1015,10 +1113,10 @@
         <v>标准杯</v>
       </c>
       <c r="R7" t="str">
-        <v>超高齿比 (XH/XG)</v>
+        <v>超高速比 (XH/XG)</v>
       </c>
       <c r="S7" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1026,7 +1124,7 @@
         <v/>
       </c>
       <c r="B8" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-ソルティガ-2025</v>
       </c>
       <c r="C8" t="str">
         <v>SALTIGA 18000-H</v>
@@ -1074,10 +1172,10 @@
         <v>标准杯</v>
       </c>
       <c r="R8" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S8" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1085,7 +1183,7 @@
         <v/>
       </c>
       <c r="B9" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-ソルティガ-2025</v>
       </c>
       <c r="C9" t="str">
         <v>SALTIGA 20000-P</v>
@@ -1133,10 +1231,10 @@
         <v>标准杯</v>
       </c>
       <c r="R9" t="str">
-        <v>低齿比 (P/PG)</v>
+        <v>低速比 (P/PG)</v>
       </c>
       <c r="S9" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1144,7 +1242,7 @@
         <v/>
       </c>
       <c r="B10" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-ソルティガ-2025</v>
       </c>
       <c r="C10" t="str">
         <v>SALTIGA 20000-H</v>
@@ -1192,10 +1290,10 @@
         <v>标准杯</v>
       </c>
       <c r="R10" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S10" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1203,7 +1301,7 @@
         <v/>
       </c>
       <c r="B11" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-ソルティガ-2025</v>
       </c>
       <c r="C11" t="str">
         <v>SALTIGA 25000-P</v>
@@ -1251,10 +1349,10 @@
         <v>标准杯</v>
       </c>
       <c r="R11" t="str">
-        <v>低齿比 (P/PG)</v>
+        <v>低速比 (P/PG)</v>
       </c>
       <c r="S11" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1262,7 +1360,7 @@
         <v/>
       </c>
       <c r="B12" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-ソルティガ-2025</v>
       </c>
       <c r="C12" t="str">
         <v>SALTIGA 30000-P</v>
@@ -1310,10 +1408,10 @@
         <v>标准杯</v>
       </c>
       <c r="R12" t="str">
-        <v>低齿比 (P/PG)</v>
+        <v>低速比 (P/PG)</v>
       </c>
       <c r="S12" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1321,7 +1419,7 @@
         <v/>
       </c>
       <c r="B13" t="str">
-        <v>R-DA-ソルティガ</v>
+        <v>R-DA-ソルティガ-2025</v>
       </c>
       <c r="C13" t="str">
         <v>SALTIGA 30000-H</v>
@@ -1369,10 +1467,10 @@
         <v>标准杯</v>
       </c>
       <c r="R13" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S13" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1380,7 +1478,7 @@
         <v/>
       </c>
       <c r="B14" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="C14" t="str">
         <v>4000-H</v>
@@ -1428,10 +1526,10 @@
         <v>标准杯</v>
       </c>
       <c r="R14" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S14" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1439,7 +1537,7 @@
         <v/>
       </c>
       <c r="B15" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="C15" t="str">
         <v>4000-XH</v>
@@ -1487,10 +1585,10 @@
         <v>标准杯</v>
       </c>
       <c r="R15" t="str">
-        <v>超高齿比 (XH/XG)</v>
+        <v>超高速比 (XH/XG)</v>
       </c>
       <c r="S15" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1498,7 +1596,7 @@
         <v/>
       </c>
       <c r="B16" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="C16" t="str">
         <v>5000-P</v>
@@ -1546,10 +1644,10 @@
         <v>标准杯</v>
       </c>
       <c r="R16" t="str">
-        <v>低齿比 (P/PG)</v>
+        <v>低速比 (P/PG)</v>
       </c>
       <c r="S16" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1557,7 +1655,7 @@
         <v/>
       </c>
       <c r="B17" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="C17" t="str">
         <v>5000-H</v>
@@ -1605,10 +1703,10 @@
         <v>标准杯</v>
       </c>
       <c r="R17" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S17" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1616,7 +1714,7 @@
         <v/>
       </c>
       <c r="B18" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="C18" t="str">
         <v>5000-XH</v>
@@ -1664,10 +1762,10 @@
         <v>标准杯</v>
       </c>
       <c r="R18" t="str">
-        <v>超高齿比 (XH/XG)</v>
+        <v>超高速比 (XH/XG)</v>
       </c>
       <c r="S18" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1675,7 +1773,7 @@
         <v/>
       </c>
       <c r="B19" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="C19" t="str">
         <v>6000-P</v>
@@ -1723,10 +1821,10 @@
         <v>标准杯</v>
       </c>
       <c r="R19" t="str">
-        <v>低齿比 (P/PG)</v>
+        <v>低速比 (P/PG)</v>
       </c>
       <c r="S19" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1734,7 +1832,7 @@
         <v/>
       </c>
       <c r="B20" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="C20" t="str">
         <v>6000-H</v>
@@ -1782,10 +1880,10 @@
         <v>标准杯</v>
       </c>
       <c r="R20" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S20" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1793,7 +1891,7 @@
         <v/>
       </c>
       <c r="B21" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="C21" t="str">
         <v>6000-XH</v>
@@ -1841,10 +1939,10 @@
         <v>标准杯</v>
       </c>
       <c r="R21" t="str">
-        <v>超高齿比 (XH/XG)</v>
+        <v>超高速比 (XH/XG)</v>
       </c>
       <c r="S21" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1852,7 +1950,7 @@
         <v/>
       </c>
       <c r="B22" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="C22" t="str">
         <v>ソルティガ 4000-H</v>
@@ -1900,10 +1998,10 @@
         <v>标准杯</v>
       </c>
       <c r="R22" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S22" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1911,7 +2009,7 @@
         <v/>
       </c>
       <c r="B23" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="C23" t="str">
         <v>ソルティガ 4000-XH</v>
@@ -1959,10 +2057,10 @@
         <v>标准杯</v>
       </c>
       <c r="R23" t="str">
-        <v>超高齿比 (XH/XG)</v>
+        <v>超高速比 (XH/XG)</v>
       </c>
       <c r="S23" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1970,7 +2068,7 @@
         <v/>
       </c>
       <c r="B24" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="C24" t="str">
         <v>ソルティガ 5000-P</v>
@@ -2018,10 +2116,10 @@
         <v>标准杯</v>
       </c>
       <c r="R24" t="str">
-        <v>低齿比 (P/PG)</v>
+        <v>低速比 (P/PG)</v>
       </c>
       <c r="S24" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -2029,7 +2127,7 @@
         <v/>
       </c>
       <c r="B25" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="C25" t="str">
         <v>ソルティガ 5000-H</v>
@@ -2077,10 +2175,10 @@
         <v>标准杯</v>
       </c>
       <c r="R25" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S25" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -2088,7 +2186,7 @@
         <v/>
       </c>
       <c r="B26" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="C26" t="str">
         <v>ソルティガ 5000-XH</v>
@@ -2136,10 +2234,10 @@
         <v>标准杯</v>
       </c>
       <c r="R26" t="str">
-        <v>超高齿比 (XH/XG)</v>
+        <v>超高速比 (XH/XG)</v>
       </c>
       <c r="S26" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -2147,7 +2245,7 @@
         <v/>
       </c>
       <c r="B27" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="C27" t="str">
         <v>ソルティガ 6000-P</v>
@@ -2195,10 +2293,10 @@
         <v>标准杯</v>
       </c>
       <c r="R27" t="str">
-        <v>低齿比 (P/PG)</v>
+        <v>低速比 (P/PG)</v>
       </c>
       <c r="S27" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -2206,7 +2304,7 @@
         <v/>
       </c>
       <c r="B28" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="C28" t="str">
         <v>ソルティガ 6000-H</v>
@@ -2254,10 +2352,10 @@
         <v>标准杯</v>
       </c>
       <c r="R28" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S28" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -2265,7 +2363,7 @@
         <v/>
       </c>
       <c r="B29" t="str">
-        <v>R-DA-ソルティガ-4000/5000/6000</v>
+        <v>R-DA-ソルティガ-2023</v>
       </c>
       <c r="C29" t="str">
         <v>ソルティガ 6000-XH</v>
@@ -2313,10 +2411,10 @@
         <v>标准杯</v>
       </c>
       <c r="R29" t="str">
-        <v>超高齿比 (XH/XG)</v>
+        <v>超高速比 (XH/XG)</v>
       </c>
       <c r="S29" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -2324,7 +2422,7 @@
         <v/>
       </c>
       <c r="B30" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C30" t="str">
         <v>LT2000S-P</v>
@@ -2372,10 +2470,10 @@
         <v>浅杯 (S)</v>
       </c>
       <c r="R30" t="str">
-        <v>低齿比 (P/PG)</v>
+        <v>低速比 (P/PG)</v>
       </c>
       <c r="S30" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -2383,7 +2481,7 @@
         <v/>
       </c>
       <c r="B31" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C31" t="str">
         <v>LT2000S-H</v>
@@ -2431,10 +2529,10 @@
         <v>浅杯 (S)</v>
       </c>
       <c r="R31" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S31" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -2442,7 +2540,7 @@
         <v/>
       </c>
       <c r="B32" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C32" t="str">
         <v>LT2500S</v>
@@ -2490,10 +2588,10 @@
         <v>浅杯 (S)</v>
       </c>
       <c r="R32" t="str">
-        <v>标准齿比</v>
+        <v>标准速比</v>
       </c>
       <c r="S32" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -2501,7 +2599,7 @@
         <v/>
       </c>
       <c r="B33" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C33" t="str">
         <v>LT2500S-H</v>
@@ -2549,10 +2647,10 @@
         <v>浅杯 (S)</v>
       </c>
       <c r="R33" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S33" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -2560,7 +2658,7 @@
         <v/>
       </c>
       <c r="B34" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C34" t="str">
         <v>LT2500S-XH</v>
@@ -2608,10 +2706,10 @@
         <v>浅杯 (S)</v>
       </c>
       <c r="R34" t="str">
-        <v>超高齿比 (XH/XG)</v>
+        <v>超高速比 (XH/XG)</v>
       </c>
       <c r="S34" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -2619,7 +2717,7 @@
         <v/>
       </c>
       <c r="B35" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C35" t="str">
         <v>LT2500S-DH</v>
@@ -2667,10 +2765,10 @@
         <v>浅杯 (S)</v>
       </c>
       <c r="R35" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S35" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -2678,7 +2776,7 @@
         <v/>
       </c>
       <c r="B36" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C36" t="str">
         <v>PC LT2500</v>
@@ -2726,10 +2824,10 @@
         <v>标准杯</v>
       </c>
       <c r="R36" t="str">
-        <v>低齿比 (P/PG)</v>
+        <v>低速比 (P/PG)</v>
       </c>
       <c r="S36" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -2737,7 +2835,7 @@
         <v/>
       </c>
       <c r="B37" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C37" t="str">
         <v>PC LT2500-H</v>
@@ -2785,10 +2883,10 @@
         <v>标准杯</v>
       </c>
       <c r="R37" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S37" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -2796,7 +2894,7 @@
         <v/>
       </c>
       <c r="B38" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C38" t="str">
         <v>LT3000S</v>
@@ -2844,10 +2942,10 @@
         <v>浅杯 (S)</v>
       </c>
       <c r="R38" t="str">
-        <v>标准齿比</v>
+        <v>标准速比</v>
       </c>
       <c r="S38" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -2855,7 +2953,7 @@
         <v/>
       </c>
       <c r="B39" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C39" t="str">
         <v>LT3000-H</v>
@@ -2903,10 +3001,10 @@
         <v>标准杯</v>
       </c>
       <c r="R39" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S39" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -2914,7 +3012,7 @@
         <v/>
       </c>
       <c r="B40" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C40" t="str">
         <v>PC LT3000</v>
@@ -2962,10 +3060,10 @@
         <v>标准杯</v>
       </c>
       <c r="R40" t="str">
-        <v>低齿比 (P/PG)</v>
+        <v>低速比 (P/PG)</v>
       </c>
       <c r="S40" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -2973,7 +3071,7 @@
         <v/>
       </c>
       <c r="B41" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C41" t="str">
         <v>PC LT3000-XH</v>
@@ -3021,10 +3119,10 @@
         <v>标准杯</v>
       </c>
       <c r="R41" t="str">
-        <v>超高齿比 (XH/XG)</v>
+        <v>超高速比 (XH/XG)</v>
       </c>
       <c r="S41" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -3032,7 +3130,7 @@
         <v/>
       </c>
       <c r="B42" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C42" t="str">
         <v>LT4000</v>
@@ -3080,10 +3178,10 @@
         <v>标准杯</v>
       </c>
       <c r="R42" t="str">
-        <v>标准齿比</v>
+        <v>标准速比</v>
       </c>
       <c r="S42" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -3091,7 +3189,7 @@
         <v/>
       </c>
       <c r="B43" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C43" t="str">
         <v>LT4000-XH</v>
@@ -3139,10 +3237,10 @@
         <v>标准杯</v>
       </c>
       <c r="R43" t="str">
-        <v>超高齿比 (XH/XG)</v>
+        <v>超高速比 (XH/XG)</v>
       </c>
       <c r="S43" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -3150,7 +3248,7 @@
         <v/>
       </c>
       <c r="B44" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C44" t="str">
         <v>LT5000-C</v>
@@ -3198,10 +3296,10 @@
         <v>标准杯</v>
       </c>
       <c r="R44" t="str">
-        <v>标准齿比</v>
+        <v>标准速比</v>
       </c>
       <c r="S44" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -3209,7 +3307,7 @@
         <v/>
       </c>
       <c r="B45" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C45" t="str">
         <v>LT5000-CXH</v>
@@ -3257,10 +3355,10 @@
         <v>标准杯</v>
       </c>
       <c r="R45" t="str">
-        <v>超高齿比 (XH/XG)</v>
+        <v>超高速比 (XH/XG)</v>
       </c>
       <c r="S45" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -3268,7 +3366,7 @@
         <v/>
       </c>
       <c r="B46" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C46" t="str">
         <v>SF1000S-P</v>
@@ -3316,10 +3414,10 @@
         <v>浅杯 (S)</v>
       </c>
       <c r="R46" t="str">
-        <v>低齿比 (P/PG)</v>
+        <v>低速比 (P/PG)</v>
       </c>
       <c r="S46" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -3327,7 +3425,7 @@
         <v/>
       </c>
       <c r="B47" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C47" t="str">
         <v>SF2000SS-P</v>
@@ -3375,10 +3473,10 @@
         <v>极浅杯 (SS)</v>
       </c>
       <c r="R47" t="str">
-        <v>低齿比 (P/PG)</v>
+        <v>低速比 (P/PG)</v>
       </c>
       <c r="S47" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -3386,7 +3484,7 @@
         <v/>
       </c>
       <c r="B48" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C48" t="str">
         <v>SF2000SS-H</v>
@@ -3434,10 +3532,10 @@
         <v>极浅杯 (SS)</v>
       </c>
       <c r="R48" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S48" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -3445,7 +3543,7 @@
         <v/>
       </c>
       <c r="B49" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C49" t="str">
         <v>SF2500SS</v>
@@ -3493,10 +3591,10 @@
         <v>极浅杯 (SS)</v>
       </c>
       <c r="R49" t="str">
-        <v>标准齿比</v>
+        <v>标准速比</v>
       </c>
       <c r="S49" t="str">
-        <v>无</v>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -3504,7 +3602,7 @@
         <v/>
       </c>
       <c r="B50" t="str">
-        <v>R-DA-EXIST</v>
+        <v>R-DA-EXIST-2022</v>
       </c>
       <c r="C50" t="str">
         <v>SF2500SS-H</v>
@@ -3552,15 +3650,723 @@
         <v>极浅杯 (SS)</v>
       </c>
       <c r="R50" t="str">
-        <v>高齿比 (H/HG)</v>
+        <v>高速比 (H/HG)</v>
       </c>
       <c r="S50" t="str">
-        <v>无</v>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v/>
+      </c>
+      <c r="B51" t="str">
+        <v>R-DA-セルテート-SW-2026</v>
+      </c>
+      <c r="C51" t="str">
+        <v>セルテート SW 8000-P</v>
+      </c>
+      <c r="D51" t="str">
+        <v>セルテート SW 8000-P</v>
+      </c>
+      <c r="E51" t="str">
+        <v>2026</v>
+      </c>
+      <c r="F51" t="str">
+        <v>8000</v>
+      </c>
+      <c r="G51" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="H51">
+        <v>655</v>
+      </c>
+      <c r="I51" t="str">
+        <v>25</v>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v>3-460_4-300</v>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
+        <v>80</v>
+      </c>
+      <c r="O51" t="str">
+        <v>9(9/1)</v>
+      </c>
+      <c r="P51" t="str">
+        <v>93,100</v>
+      </c>
+      <c r="Q51" t="str">
+        <v>标准杯</v>
+      </c>
+      <c r="R51" t="str">
+        <v>低速比 (P/PG)</v>
+      </c>
+      <c r="S51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v/>
+      </c>
+      <c r="B52" t="str">
+        <v>R-DA-セルテート-SW-2026</v>
+      </c>
+      <c r="C52" t="str">
+        <v>セルテート SW 8000-H</v>
+      </c>
+      <c r="D52" t="str">
+        <v>セルテート SW 8000-H</v>
+      </c>
+      <c r="E52" t="str">
+        <v>2026</v>
+      </c>
+      <c r="F52" t="str">
+        <v>8000</v>
+      </c>
+      <c r="G52" t="str">
+        <v>5.6</v>
+      </c>
+      <c r="H52">
+        <v>665</v>
+      </c>
+      <c r="I52" t="str">
+        <v>25</v>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v>3-460_4-300</v>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
+        <v>80</v>
+      </c>
+      <c r="O52" t="str">
+        <v>9(9/1)</v>
+      </c>
+      <c r="P52" t="str">
+        <v>93,100</v>
+      </c>
+      <c r="Q52" t="str">
+        <v>标准杯</v>
+      </c>
+      <c r="R52" t="str">
+        <v>高速比 (H/HG)</v>
+      </c>
+      <c r="S52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v/>
+      </c>
+      <c r="B53" t="str">
+        <v>R-DA-セルテート-SW-2026</v>
+      </c>
+      <c r="C53" t="str">
+        <v>セルテート SW 10000-P</v>
+      </c>
+      <c r="D53" t="str">
+        <v>セルテート SW 10000-P</v>
+      </c>
+      <c r="E53" t="str">
+        <v>2026</v>
+      </c>
+      <c r="F53" t="str">
+        <v>10000</v>
+      </c>
+      <c r="G53" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="H53">
+        <v>660</v>
+      </c>
+      <c r="I53" t="str">
+        <v>25</v>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v>4-380_5-300</v>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
+        <v>85</v>
+      </c>
+      <c r="O53" t="str">
+        <v>9(9/1)</v>
+      </c>
+      <c r="P53" t="str">
+        <v>93,100</v>
+      </c>
+      <c r="Q53" t="str">
+        <v>标准杯</v>
+      </c>
+      <c r="R53" t="str">
+        <v>低速比 (P/PG)</v>
+      </c>
+      <c r="S53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v/>
+      </c>
+      <c r="B54" t="str">
+        <v>R-DA-セルテート-SW-2026</v>
+      </c>
+      <c r="C54" t="str">
+        <v>セルテート SW 10000-H</v>
+      </c>
+      <c r="D54" t="str">
+        <v>セルテート SW 10000-H</v>
+      </c>
+      <c r="E54" t="str">
+        <v>2026</v>
+      </c>
+      <c r="F54" t="str">
+        <v>10000</v>
+      </c>
+      <c r="G54" t="str">
+        <v>5.6</v>
+      </c>
+      <c r="H54">
+        <v>670</v>
+      </c>
+      <c r="I54" t="str">
+        <v>25</v>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v>4-380_5-300</v>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
+        <v>85</v>
+      </c>
+      <c r="O54" t="str">
+        <v>9(9/1)</v>
+      </c>
+      <c r="P54" t="str">
+        <v>93,100</v>
+      </c>
+      <c r="Q54" t="str">
+        <v>标准杯</v>
+      </c>
+      <c r="R54" t="str">
+        <v>高速比 (H/HG)</v>
+      </c>
+      <c r="S54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v/>
+      </c>
+      <c r="B55" t="str">
+        <v>R-DA-セルテート-SW-2026</v>
+      </c>
+      <c r="C55" t="str">
+        <v>セルテート SW 14000-P</v>
+      </c>
+      <c r="D55" t="str">
+        <v>セルテート SW 14000-P</v>
+      </c>
+      <c r="E55" t="str">
+        <v>2026</v>
+      </c>
+      <c r="F55" t="str">
+        <v>14000</v>
+      </c>
+      <c r="G55" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="H55">
+        <v>675</v>
+      </c>
+      <c r="I55" t="str">
+        <v>25</v>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v>5-340_6-300</v>
+      </c>
+      <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
+        <v>85</v>
+      </c>
+      <c r="O55" t="str">
+        <v>9(9/1)</v>
+      </c>
+      <c r="P55" t="str">
+        <v>93,100</v>
+      </c>
+      <c r="Q55" t="str">
+        <v>标准杯</v>
+      </c>
+      <c r="R55" t="str">
+        <v>低速比 (P/PG)</v>
+      </c>
+      <c r="S55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v/>
+      </c>
+      <c r="B56" t="str">
+        <v>R-DA-セルテート-SW-2026</v>
+      </c>
+      <c r="C56" t="str">
+        <v>セルテート SW 14000-XH</v>
+      </c>
+      <c r="D56" t="str">
+        <v>セルテート SW 14000-XH</v>
+      </c>
+      <c r="E56" t="str">
+        <v>2026</v>
+      </c>
+      <c r="F56" t="str">
+        <v>14000</v>
+      </c>
+      <c r="G56" t="str">
+        <v>6.2</v>
+      </c>
+      <c r="H56">
+        <v>675</v>
+      </c>
+      <c r="I56" t="str">
+        <v>25</v>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v>5-340_6-300</v>
+      </c>
+      <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
+        <v>85</v>
+      </c>
+      <c r="O56" t="str">
+        <v>9(9/1)</v>
+      </c>
+      <c r="P56" t="str">
+        <v>93,100</v>
+      </c>
+      <c r="Q56" t="str">
+        <v>标准杯</v>
+      </c>
+      <c r="R56" t="str">
+        <v>超高速比 (XH/XG)</v>
+      </c>
+      <c r="S56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v/>
+      </c>
+      <c r="B57" t="str">
+        <v>R-DA-セルテート-SW-2026</v>
+      </c>
+      <c r="C57" t="str">
+        <v>セルテート SW 18000-H</v>
+      </c>
+      <c r="D57" t="str">
+        <v>セルテート SW 18000-H</v>
+      </c>
+      <c r="E57" t="str">
+        <v>2026</v>
+      </c>
+      <c r="F57" t="str">
+        <v>18000</v>
+      </c>
+      <c r="G57" t="str">
+        <v>5.5</v>
+      </c>
+      <c r="H57">
+        <v>885</v>
+      </c>
+      <c r="I57" t="str">
+        <v>30</v>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v>6-420_8-300</v>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
+        <v>90</v>
+      </c>
+      <c r="O57" t="str">
+        <v>9(9/1)</v>
+      </c>
+      <c r="P57" t="str">
+        <v>104,500</v>
+      </c>
+      <c r="Q57" t="str">
+        <v>标准杯</v>
+      </c>
+      <c r="R57" t="str">
+        <v>高速比 (H/HG)</v>
+      </c>
+      <c r="S57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v/>
+      </c>
+      <c r="B58" t="str">
+        <v>R-DA-セルテート-SW-2026</v>
+      </c>
+      <c r="C58" t="str">
+        <v>セルテート SW 20000-P</v>
+      </c>
+      <c r="D58" t="str">
+        <v>セルテート SW 20000-P</v>
+      </c>
+      <c r="E58" t="str">
+        <v>2026</v>
+      </c>
+      <c r="F58" t="str">
+        <v>20000</v>
+      </c>
+      <c r="G58" t="str">
+        <v>4.4</v>
+      </c>
+      <c r="H58">
+        <v>895</v>
+      </c>
+      <c r="I58" t="str">
+        <v>30</v>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v>8-370_10-300</v>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
+        <v>90</v>
+      </c>
+      <c r="O58" t="str">
+        <v>9(9/1)</v>
+      </c>
+      <c r="P58" t="str">
+        <v>104,500</v>
+      </c>
+      <c r="Q58" t="str">
+        <v>标准杯</v>
+      </c>
+      <c r="R58" t="str">
+        <v>低速比 (P/PG)</v>
+      </c>
+      <c r="S58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v/>
+      </c>
+      <c r="B59" t="str">
+        <v>R-DA-セルテート-SW-2026</v>
+      </c>
+      <c r="C59" t="str">
+        <v>セルテート SW 20000-H</v>
+      </c>
+      <c r="D59" t="str">
+        <v>セルテート SW 20000-H</v>
+      </c>
+      <c r="E59" t="str">
+        <v>2026</v>
+      </c>
+      <c r="F59" t="str">
+        <v>20000</v>
+      </c>
+      <c r="G59" t="str">
+        <v>5.5</v>
+      </c>
+      <c r="H59">
+        <v>895</v>
+      </c>
+      <c r="I59" t="str">
+        <v>30</v>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v>8-370_10-300</v>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
+        <v>90</v>
+      </c>
+      <c r="O59" t="str">
+        <v>9(9/1)</v>
+      </c>
+      <c r="P59" t="str">
+        <v>104,500</v>
+      </c>
+      <c r="Q59" t="str">
+        <v>标准杯</v>
+      </c>
+      <c r="R59" t="str">
+        <v>高速比 (H/HG)</v>
+      </c>
+      <c r="S59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v/>
+      </c>
+      <c r="B60" t="str">
+        <v>R-DA-トーナメントサーフ-45-2019</v>
+      </c>
+      <c r="C60" t="str">
+        <v>トーナメントサーフ45 HG 05PE</v>
+      </c>
+      <c r="D60" t="str">
+        <v>トーナメントサーフ45 HG 05PE</v>
+      </c>
+      <c r="E60" t="str">
+        <v>2019</v>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v>4.9</v>
+      </c>
+      <c r="H60">
+        <v>395</v>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v>0.3-300_0.5-250</v>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v>85</v>
+      </c>
+      <c r="O60" t="str">
+        <v>10/1</v>
+      </c>
+      <c r="P60" t="str">
+        <v>98,000</v>
+      </c>
+      <c r="Q60" t="str">
+        <v>标准杯</v>
+      </c>
+      <c r="R60" t="str">
+        <v>高速比 (H/HG)</v>
+      </c>
+      <c r="S60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v/>
+      </c>
+      <c r="B61" t="str">
+        <v>R-DA-トーナメントサーフ-45-2019</v>
+      </c>
+      <c r="C61" t="str">
+        <v>トーナメントサーフ45 06PE</v>
+      </c>
+      <c r="D61" t="str">
+        <v>トーナメントサーフ45 06PE</v>
+      </c>
+      <c r="E61" t="str">
+        <v>2019</v>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v>4.1</v>
+      </c>
+      <c r="H61">
+        <v>400</v>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v>0.6-250_0.8-200</v>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
+        <v>85</v>
+      </c>
+      <c r="O61" t="str">
+        <v>10/1</v>
+      </c>
+      <c r="P61" t="str">
+        <v>98,000</v>
+      </c>
+      <c r="Q61" t="str">
+        <v>标准杯</v>
+      </c>
+      <c r="R61" t="str">
+        <v>低速比 (P/PG)</v>
+      </c>
+      <c r="S61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v/>
+      </c>
+      <c r="B62" t="str">
+        <v>R-DA-トーナメントサーフ-45-2019</v>
+      </c>
+      <c r="C62" t="str">
+        <v>トーナメントサーフ45 LG 06PE</v>
+      </c>
+      <c r="D62" t="str">
+        <v>トーナメントサーフ45 LG 06PE</v>
+      </c>
+      <c r="E62" t="str">
+        <v>2019</v>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="H62">
+        <v>400</v>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v>0.6-250_0.8-200</v>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
+        <v>85</v>
+      </c>
+      <c r="O62" t="str">
+        <v>10/1</v>
+      </c>
+      <c r="P62" t="str">
+        <v>98,000</v>
+      </c>
+      <c r="Q62" t="str">
+        <v>标准杯</v>
+      </c>
+      <c r="R62" t="str">
+        <v>低速比 (P/PG)</v>
+      </c>
+      <c r="S62" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S62"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/pkgGear/data_raw/daiwa_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_reels_import.xlsx
@@ -492,10 +492,10 @@
         <v>在售</v>
       </c>
       <c r="N2" t="str">
-        <v>2026-04-03 18:54:42</v>
+        <v>2026-04-04 01:39:23</v>
       </c>
       <c r="O2" t="str">
-        <v>2026-04-03 18:54:42</v>
+        <v>2026-04-04 01:39:23</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -541,10 +541,10 @@
         <v>在售</v>
       </c>
       <c r="N3" t="str">
-        <v>2026-04-03 18:54:42</v>
+        <v>2026-04-04 01:39:23</v>
       </c>
       <c r="O3" t="str">
-        <v>2026-04-03 18:54:42</v>
+        <v>2026-04-04 01:39:23</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -591,10 +591,10 @@
         <v>在售</v>
       </c>
       <c r="N4" t="str">
-        <v>2026-04-03 18:54:42</v>
+        <v>2026-04-04 01:39:23</v>
       </c>
       <c r="O4" t="str">
-        <v>2026-04-03 18:54:42</v>
+        <v>2026-04-04 01:39:23</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -641,10 +641,10 @@
         <v>在售</v>
       </c>
       <c r="N5" t="str">
-        <v>2026-04-03 18:54:42</v>
+        <v>2026-04-04 01:39:23</v>
       </c>
       <c r="O5" t="str">
-        <v>2026-04-03 18:54:42</v>
+        <v>2026-04-04 01:39:23</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -689,10 +689,10 @@
         <v>在售</v>
       </c>
       <c r="N6" t="str">
-        <v>2026-04-03 18:54:42</v>
+        <v>2026-04-04 01:39:23</v>
       </c>
       <c r="O6" t="str">
-        <v>2026-04-03 18:54:42</v>
+        <v>2026-04-04 01:39:23</v>
       </c>
     </row>
   </sheetData>
@@ -704,7 +704,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S62"/>
+  <dimension ref="A1:W62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -744,16 +744,16 @@
         <v>line_capacity_nylon</v>
       </c>
       <c r="M1" t="str">
-        <v>cm_per_turn</v>
+        <v>retrieve_per_turn_cm</v>
       </c>
       <c r="N1" t="str">
         <v>handle_length_mm</v>
       </c>
       <c r="O1" t="str">
-        <v>bearing_count_roller</v>
+        <v>bearing_count_main</v>
       </c>
       <c r="P1" t="str">
-        <v>market_reference_price</v>
+        <v>official_reference_price</v>
       </c>
       <c r="Q1" t="str">
         <v>spool_depth_normalized</v>
@@ -764,6 +764,18 @@
       <c r="S1" t="str">
         <v>brake_type_normalized</v>
       </c>
+      <c r="T1" t="str">
+        <v>fit_style_tags</v>
+      </c>
+      <c r="U1" t="str">
+        <v>min_lure_weight_hint</v>
+      </c>
+      <c r="V1" t="str">
+        <v>is_compact_body</v>
+      </c>
+      <c r="W1" t="str">
+        <v>handle_style</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -794,7 +806,7 @@
         <v>25</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K2" t="str">
         <v>3-460_4-300</v>
@@ -803,7 +815,7 @@
         <v/>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>94</v>
       </c>
       <c r="N2" t="str">
         <v>80</v>
@@ -818,9 +830,21 @@
         <v>标准杯</v>
       </c>
       <c r="R2" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v>SALTIGA</v>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v/>
+      </c>
+      <c r="W2" t="str">
         <v/>
       </c>
     </row>
@@ -853,7 +877,7 @@
         <v>25</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K3" t="str">
         <v>3-460_4-300</v>
@@ -862,7 +886,7 @@
         <v/>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>110</v>
       </c>
       <c r="N3" t="str">
         <v>80</v>
@@ -877,9 +901,21 @@
         <v>标准杯</v>
       </c>
       <c r="R3" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v>SALTIGA</v>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
+      <c r="W3" t="str">
         <v/>
       </c>
     </row>
@@ -912,7 +948,7 @@
         <v>25</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K4" t="str">
         <v>4-380_5-300</v>
@@ -921,7 +957,7 @@
         <v/>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>99</v>
       </c>
       <c r="N4" t="str">
         <v>85</v>
@@ -936,9 +972,21 @@
         <v>标准杯</v>
       </c>
       <c r="R4" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v>SALTIGA</v>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v/>
+      </c>
+      <c r="W4" t="str">
         <v/>
       </c>
     </row>
@@ -971,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K5" t="str">
         <v>4-380_5-300</v>
@@ -980,7 +1028,7 @@
         <v/>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>117</v>
       </c>
       <c r="N5" t="str">
         <v>85</v>
@@ -995,9 +1043,21 @@
         <v>标准杯</v>
       </c>
       <c r="R5" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v>SALTIGA</v>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
         <v/>
       </c>
     </row>
@@ -1030,7 +1090,7 @@
         <v>25</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K6" t="str">
         <v>5-340_6-300</v>
@@ -1039,7 +1099,7 @@
         <v/>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>102</v>
       </c>
       <c r="N6" t="str">
         <v>85</v>
@@ -1054,9 +1114,21 @@
         <v>标准杯</v>
       </c>
       <c r="R6" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S6" t="str">
+        <v/>
+      </c>
+      <c r="T6" t="str">
+        <v>SALTIGA</v>
+      </c>
+      <c r="U6" t="str">
+        <v/>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
         <v/>
       </c>
     </row>
@@ -1089,7 +1161,7 @@
         <v>25</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K7" t="str">
         <v>5-340_6-300</v>
@@ -1098,7 +1170,7 @@
         <v/>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>133</v>
       </c>
       <c r="N7" t="str">
         <v>85</v>
@@ -1113,9 +1185,21 @@
         <v>标准杯</v>
       </c>
       <c r="R7" t="str">
-        <v>超高速比 (XH/XG)</v>
+        <v>超高速比 (XH)</v>
       </c>
       <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v>SALTIGA</v>
+      </c>
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
         <v/>
       </c>
     </row>
@@ -1148,7 +1232,7 @@
         <v>30</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K8" t="str">
         <v>6-420_8-300</v>
@@ -1157,7 +1241,7 @@
         <v/>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>129</v>
       </c>
       <c r="N8" t="str">
         <v>90</v>
@@ -1172,9 +1256,21 @@
         <v>标准杯</v>
       </c>
       <c r="R8" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v>SALTIGA</v>
+      </c>
+      <c r="U8" t="str">
+        <v/>
+      </c>
+      <c r="V8" t="str">
+        <v/>
+      </c>
+      <c r="W8" t="str">
         <v/>
       </c>
     </row>
@@ -1207,7 +1303,7 @@
         <v>30</v>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K9" t="str">
         <v>8-370_10-300</v>
@@ -1216,7 +1312,7 @@
         <v/>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>111</v>
       </c>
       <c r="N9" t="str">
         <v>90</v>
@@ -1231,9 +1327,21 @@
         <v>标准杯</v>
       </c>
       <c r="R9" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v>SALTIGA</v>
+      </c>
+      <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <v/>
+      </c>
+      <c r="W9" t="str">
         <v/>
       </c>
     </row>
@@ -1266,7 +1374,7 @@
         <v>30</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K10" t="str">
         <v>8-370_10-300</v>
@@ -1275,7 +1383,7 @@
         <v/>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>138</v>
       </c>
       <c r="N10" t="str">
         <v>90</v>
@@ -1290,9 +1398,21 @@
         <v>标准杯</v>
       </c>
       <c r="R10" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v>SALTIGA</v>
+      </c>
+      <c r="U10" t="str">
+        <v/>
+      </c>
+      <c r="V10" t="str">
+        <v/>
+      </c>
+      <c r="W10" t="str">
         <v/>
       </c>
     </row>
@@ -1325,7 +1445,7 @@
         <v>30</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K11" t="str">
         <v>10-360_12-300</v>
@@ -1334,7 +1454,7 @@
         <v/>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>118</v>
       </c>
       <c r="N11" t="str">
         <v>90</v>
@@ -1349,9 +1469,21 @@
         <v>标准杯</v>
       </c>
       <c r="R11" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v>SALTIGA</v>
+      </c>
+      <c r="U11" t="str">
+        <v/>
+      </c>
+      <c r="V11" t="str">
+        <v/>
+      </c>
+      <c r="W11" t="str">
         <v/>
       </c>
     </row>
@@ -1384,7 +1516,7 @@
         <v>30</v>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K12" t="str">
         <v>12-400_15-300</v>
@@ -1393,7 +1525,7 @@
         <v/>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>125</v>
       </c>
       <c r="N12" t="str">
         <v>95</v>
@@ -1408,9 +1540,21 @@
         <v>标准杯</v>
       </c>
       <c r="R12" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S12" t="str">
+        <v/>
+      </c>
+      <c r="T12" t="str">
+        <v>SALTIGA</v>
+      </c>
+      <c r="U12" t="str">
+        <v/>
+      </c>
+      <c r="V12" t="str">
+        <v/>
+      </c>
+      <c r="W12" t="str">
         <v/>
       </c>
     </row>
@@ -1443,7 +1587,7 @@
         <v>30</v>
       </c>
       <c r="J13" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K13" t="str">
         <v>12-400_15-300</v>
@@ -1452,7 +1596,7 @@
         <v/>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>155</v>
       </c>
       <c r="N13" t="str">
         <v>95</v>
@@ -1467,9 +1611,21 @@
         <v>标准杯</v>
       </c>
       <c r="R13" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <v>SALTIGA</v>
+      </c>
+      <c r="U13" t="str">
+        <v/>
+      </c>
+      <c r="V13" t="str">
+        <v/>
+      </c>
+      <c r="W13" t="str">
         <v/>
       </c>
     </row>
@@ -1502,7 +1658,7 @@
         <v/>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -1526,9 +1682,21 @@
         <v>标准杯</v>
       </c>
       <c r="R14" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
+      <c r="U14" t="str">
+        <v/>
+      </c>
+      <c r="V14" t="str">
+        <v/>
+      </c>
+      <c r="W14" t="str">
         <v/>
       </c>
     </row>
@@ -1561,7 +1729,7 @@
         <v/>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -1585,9 +1753,21 @@
         <v>标准杯</v>
       </c>
       <c r="R15" t="str">
-        <v>超高速比 (XH/XG)</v>
+        <v>超高速比 (XH)</v>
       </c>
       <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+      <c r="U15" t="str">
+        <v/>
+      </c>
+      <c r="V15" t="str">
+        <v/>
+      </c>
+      <c r="W15" t="str">
         <v/>
       </c>
     </row>
@@ -1620,7 +1800,7 @@
         <v/>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -1644,9 +1824,21 @@
         <v>标准杯</v>
       </c>
       <c r="R16" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S16" t="str">
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+      <c r="U16" t="str">
+        <v/>
+      </c>
+      <c r="V16" t="str">
+        <v/>
+      </c>
+      <c r="W16" t="str">
         <v/>
       </c>
     </row>
@@ -1679,7 +1871,7 @@
         <v/>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K17" t="str">
         <v/>
@@ -1703,9 +1895,21 @@
         <v>标准杯</v>
       </c>
       <c r="R17" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S17" t="str">
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <v/>
+      </c>
+      <c r="U17" t="str">
+        <v/>
+      </c>
+      <c r="V17" t="str">
+        <v/>
+      </c>
+      <c r="W17" t="str">
         <v/>
       </c>
     </row>
@@ -1738,7 +1942,7 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K18" t="str">
         <v/>
@@ -1762,9 +1966,21 @@
         <v>标准杯</v>
       </c>
       <c r="R18" t="str">
-        <v>超高速比 (XH/XG)</v>
+        <v>超高速比 (XH)</v>
       </c>
       <c r="S18" t="str">
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <v/>
+      </c>
+      <c r="U18" t="str">
+        <v/>
+      </c>
+      <c r="V18" t="str">
+        <v/>
+      </c>
+      <c r="W18" t="str">
         <v/>
       </c>
     </row>
@@ -1797,7 +2013,7 @@
         <v/>
       </c>
       <c r="J19" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K19" t="str">
         <v/>
@@ -1821,9 +2037,21 @@
         <v>标准杯</v>
       </c>
       <c r="R19" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S19" t="str">
+        <v/>
+      </c>
+      <c r="T19" t="str">
+        <v/>
+      </c>
+      <c r="U19" t="str">
+        <v/>
+      </c>
+      <c r="V19" t="str">
+        <v/>
+      </c>
+      <c r="W19" t="str">
         <v/>
       </c>
     </row>
@@ -1856,7 +2084,7 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -1880,9 +2108,21 @@
         <v>标准杯</v>
       </c>
       <c r="R20" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S20" t="str">
+        <v/>
+      </c>
+      <c r="T20" t="str">
+        <v/>
+      </c>
+      <c r="U20" t="str">
+        <v/>
+      </c>
+      <c r="V20" t="str">
+        <v/>
+      </c>
+      <c r="W20" t="str">
         <v/>
       </c>
     </row>
@@ -1915,7 +2155,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -1939,9 +2179,21 @@
         <v>标准杯</v>
       </c>
       <c r="R21" t="str">
-        <v>超高速比 (XH/XG)</v>
+        <v>超高速比 (XH)</v>
       </c>
       <c r="S21" t="str">
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <v/>
+      </c>
+      <c r="U21" t="str">
+        <v/>
+      </c>
+      <c r="V21" t="str">
+        <v/>
+      </c>
+      <c r="W21" t="str">
         <v/>
       </c>
     </row>
@@ -1974,7 +2226,7 @@
         <v>12</v>
       </c>
       <c r="J22" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K22" t="str">
         <v>2-300</v>
@@ -1983,7 +2235,7 @@
         <v/>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>90</v>
       </c>
       <c r="N22" t="str">
         <v>65</v>
@@ -1998,9 +2250,21 @@
         <v>标准杯</v>
       </c>
       <c r="R22" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S22" t="str">
+        <v/>
+      </c>
+      <c r="T22" t="str">
+        <v/>
+      </c>
+      <c r="U22" t="str">
+        <v/>
+      </c>
+      <c r="V22" t="str">
+        <v/>
+      </c>
+      <c r="W22" t="str">
         <v/>
       </c>
     </row>
@@ -2033,7 +2297,7 @@
         <v>12</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K23" t="str">
         <v>2-300</v>
@@ -2042,7 +2306,7 @@
         <v/>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>98</v>
       </c>
       <c r="N23" t="str">
         <v>65</v>
@@ -2057,9 +2321,21 @@
         <v>标准杯</v>
       </c>
       <c r="R23" t="str">
-        <v>超高速比 (XH/XG)</v>
+        <v>超高速比 (XH)</v>
       </c>
       <c r="S23" t="str">
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
+      <c r="U23" t="str">
+        <v/>
+      </c>
+      <c r="V23" t="str">
+        <v/>
+      </c>
+      <c r="W23" t="str">
         <v/>
       </c>
     </row>
@@ -2092,7 +2368,7 @@
         <v>15</v>
       </c>
       <c r="J24" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K24" t="str">
         <v>2.5-300</v>
@@ -2101,7 +2377,7 @@
         <v/>
       </c>
       <c r="M24" t="str">
-        <v/>
+        <v>82</v>
       </c>
       <c r="N24" t="str">
         <v>65</v>
@@ -2116,9 +2392,21 @@
         <v>标准杯</v>
       </c>
       <c r="R24" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S24" t="str">
+        <v/>
+      </c>
+      <c r="T24" t="str">
+        <v/>
+      </c>
+      <c r="U24" t="str">
+        <v/>
+      </c>
+      <c r="V24" t="str">
+        <v/>
+      </c>
+      <c r="W24" t="str">
         <v/>
       </c>
     </row>
@@ -2151,7 +2439,7 @@
         <v>15</v>
       </c>
       <c r="J25" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K25" t="str">
         <v>2.5-300</v>
@@ -2160,7 +2448,7 @@
         <v/>
       </c>
       <c r="M25" t="str">
-        <v/>
+        <v>96</v>
       </c>
       <c r="N25" t="str">
         <v>65</v>
@@ -2175,9 +2463,21 @@
         <v>标准杯</v>
       </c>
       <c r="R25" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S25" t="str">
+        <v/>
+      </c>
+      <c r="T25" t="str">
+        <v/>
+      </c>
+      <c r="U25" t="str">
+        <v/>
+      </c>
+      <c r="V25" t="str">
+        <v/>
+      </c>
+      <c r="W25" t="str">
         <v/>
       </c>
     </row>
@@ -2210,7 +2510,7 @@
         <v>15</v>
       </c>
       <c r="J26" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K26" t="str">
         <v>2.5-300</v>
@@ -2219,7 +2519,7 @@
         <v/>
       </c>
       <c r="M26" t="str">
-        <v/>
+        <v>104</v>
       </c>
       <c r="N26" t="str">
         <v>65</v>
@@ -2234,9 +2534,21 @@
         <v>标准杯</v>
       </c>
       <c r="R26" t="str">
-        <v>超高速比 (XH/XG)</v>
+        <v>超高速比 (XH)</v>
       </c>
       <c r="S26" t="str">
+        <v/>
+      </c>
+      <c r="T26" t="str">
+        <v/>
+      </c>
+      <c r="U26" t="str">
+        <v/>
+      </c>
+      <c r="V26" t="str">
+        <v/>
+      </c>
+      <c r="W26" t="str">
         <v/>
       </c>
     </row>
@@ -2269,7 +2581,7 @@
         <v>15</v>
       </c>
       <c r="J27" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K27" t="str">
         <v>3-300</v>
@@ -2278,7 +2590,7 @@
         <v/>
       </c>
       <c r="M27" t="str">
-        <v/>
+        <v>86</v>
       </c>
       <c r="N27" t="str">
         <v>70</v>
@@ -2293,9 +2605,21 @@
         <v>标准杯</v>
       </c>
       <c r="R27" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S27" t="str">
+        <v/>
+      </c>
+      <c r="T27" t="str">
+        <v/>
+      </c>
+      <c r="U27" t="str">
+        <v/>
+      </c>
+      <c r="V27" t="str">
+        <v/>
+      </c>
+      <c r="W27" t="str">
         <v/>
       </c>
     </row>
@@ -2328,7 +2652,7 @@
         <v>15</v>
       </c>
       <c r="J28" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K28" t="str">
         <v>3-300</v>
@@ -2337,7 +2661,7 @@
         <v/>
       </c>
       <c r="M28" t="str">
-        <v/>
+        <v>101</v>
       </c>
       <c r="N28" t="str">
         <v>70</v>
@@ -2352,9 +2676,21 @@
         <v>标准杯</v>
       </c>
       <c r="R28" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S28" t="str">
+        <v/>
+      </c>
+      <c r="T28" t="str">
+        <v/>
+      </c>
+      <c r="U28" t="str">
+        <v/>
+      </c>
+      <c r="V28" t="str">
+        <v/>
+      </c>
+      <c r="W28" t="str">
         <v/>
       </c>
     </row>
@@ -2387,7 +2723,7 @@
         <v>15</v>
       </c>
       <c r="J29" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K29" t="str">
         <v>3-300</v>
@@ -2396,7 +2732,7 @@
         <v/>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>110</v>
       </c>
       <c r="N29" t="str">
         <v>70</v>
@@ -2411,9 +2747,21 @@
         <v>标准杯</v>
       </c>
       <c r="R29" t="str">
-        <v>超高速比 (XH/XG)</v>
+        <v>超高速比 (XH)</v>
       </c>
       <c r="S29" t="str">
+        <v/>
+      </c>
+      <c r="T29" t="str">
+        <v/>
+      </c>
+      <c r="U29" t="str">
+        <v/>
+      </c>
+      <c r="V29" t="str">
+        <v/>
+      </c>
+      <c r="W29" t="str">
         <v/>
       </c>
     </row>
@@ -2446,7 +2794,7 @@
         <v>5</v>
       </c>
       <c r="J30" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K30" t="str">
         <v>0.4-200</v>
@@ -2455,7 +2803,7 @@
         <v>3-150</v>
       </c>
       <c r="M30" t="str">
-        <v/>
+        <v>64</v>
       </c>
       <c r="N30" t="str">
         <v>40</v>
@@ -2470,9 +2818,21 @@
         <v>浅杯 (S)</v>
       </c>
       <c r="R30" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S30" t="str">
+        <v/>
+      </c>
+      <c r="T30" t="str">
+        <v>LT</v>
+      </c>
+      <c r="U30" t="str">
+        <v/>
+      </c>
+      <c r="V30" t="str">
+        <v/>
+      </c>
+      <c r="W30" t="str">
         <v/>
       </c>
     </row>
@@ -2505,7 +2865,7 @@
         <v>5</v>
       </c>
       <c r="J31" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K31" t="str">
         <v>0.4-200</v>
@@ -2514,7 +2874,7 @@
         <v>3-150</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>76</v>
       </c>
       <c r="N31" t="str">
         <v>45</v>
@@ -2529,9 +2889,21 @@
         <v>浅杯 (S)</v>
       </c>
       <c r="R31" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S31" t="str">
+        <v/>
+      </c>
+      <c r="T31" t="str">
+        <v>LT</v>
+      </c>
+      <c r="U31" t="str">
+        <v/>
+      </c>
+      <c r="V31" t="str">
+        <v/>
+      </c>
+      <c r="W31" t="str">
         <v/>
       </c>
     </row>
@@ -2564,7 +2936,7 @@
         <v>5</v>
       </c>
       <c r="J32" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K32" t="str">
         <v>0.6-200</v>
@@ -2573,7 +2945,7 @@
         <v>4-150</v>
       </c>
       <c r="M32" t="str">
-        <v/>
+        <v>72</v>
       </c>
       <c r="N32" t="str">
         <v>50</v>
@@ -2588,9 +2960,21 @@
         <v>浅杯 (S)</v>
       </c>
       <c r="R32" t="str">
-        <v>标准速比</v>
+        <v>中速比</v>
       </c>
       <c r="S32" t="str">
+        <v/>
+      </c>
+      <c r="T32" t="str">
+        <v>LT</v>
+      </c>
+      <c r="U32" t="str">
+        <v/>
+      </c>
+      <c r="V32" t="str">
+        <v/>
+      </c>
+      <c r="W32" t="str">
         <v/>
       </c>
     </row>
@@ -2623,7 +3007,7 @@
         <v>5</v>
       </c>
       <c r="J33" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K33" t="str">
         <v>0.6-200</v>
@@ -2632,7 +3016,7 @@
         <v>4-150</v>
       </c>
       <c r="M33" t="str">
-        <v/>
+        <v>82</v>
       </c>
       <c r="N33" t="str">
         <v>50</v>
@@ -2647,9 +3031,21 @@
         <v>浅杯 (S)</v>
       </c>
       <c r="R33" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S33" t="str">
+        <v/>
+      </c>
+      <c r="T33" t="str">
+        <v>LT</v>
+      </c>
+      <c r="U33" t="str">
+        <v/>
+      </c>
+      <c r="V33" t="str">
+        <v/>
+      </c>
+      <c r="W33" t="str">
         <v/>
       </c>
     </row>
@@ -2682,7 +3078,7 @@
         <v>5</v>
       </c>
       <c r="J34" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K34" t="str">
         <v>0.6-200</v>
@@ -2691,7 +3087,7 @@
         <v>4-150</v>
       </c>
       <c r="M34" t="str">
-        <v/>
+        <v>87</v>
       </c>
       <c r="N34" t="str">
         <v>50</v>
@@ -2706,9 +3102,21 @@
         <v>浅杯 (S)</v>
       </c>
       <c r="R34" t="str">
-        <v>超高速比 (XH/XG)</v>
+        <v>超高速比 (XH)</v>
       </c>
       <c r="S34" t="str">
+        <v/>
+      </c>
+      <c r="T34" t="str">
+        <v>LT</v>
+      </c>
+      <c r="U34" t="str">
+        <v/>
+      </c>
+      <c r="V34" t="str">
+        <v/>
+      </c>
+      <c r="W34" t="str">
         <v/>
       </c>
     </row>
@@ -2741,7 +3149,7 @@
         <v>5</v>
       </c>
       <c r="J35" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K35" t="str">
         <v>0.6-200</v>
@@ -2750,7 +3158,7 @@
         <v>4-150</v>
       </c>
       <c r="M35" t="str">
-        <v/>
+        <v>72</v>
       </c>
       <c r="N35" t="str">
         <v>90</v>
@@ -2765,10 +3173,22 @@
         <v>浅杯 (S)</v>
       </c>
       <c r="R35" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>中速比</v>
       </c>
       <c r="S35" t="str">
         <v/>
+      </c>
+      <c r="T35" t="str">
+        <v>LT</v>
+      </c>
+      <c r="U35" t="str">
+        <v/>
+      </c>
+      <c r="V35" t="str">
+        <v/>
+      </c>
+      <c r="W35" t="str">
+        <v>双摇臂 (DH)</v>
       </c>
     </row>
     <row r="36">
@@ -2800,7 +3220,7 @@
         <v>10</v>
       </c>
       <c r="J36" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K36" t="str">
         <v>0.8-200</v>
@@ -2809,7 +3229,7 @@
         <v>6-150</v>
       </c>
       <c r="M36" t="str">
-        <v/>
+        <v>73</v>
       </c>
       <c r="N36" t="str">
         <v>50</v>
@@ -2824,9 +3244,21 @@
         <v>标准杯</v>
       </c>
       <c r="R36" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>中速比</v>
       </c>
       <c r="S36" t="str">
+        <v/>
+      </c>
+      <c r="T36" t="str">
+        <v>PC</v>
+      </c>
+      <c r="U36" t="str">
+        <v/>
+      </c>
+      <c r="V36" t="str">
+        <v/>
+      </c>
+      <c r="W36" t="str">
         <v/>
       </c>
     </row>
@@ -2859,7 +3291,7 @@
         <v>10</v>
       </c>
       <c r="J37" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K37" t="str">
         <v>0.8-200</v>
@@ -2868,7 +3300,7 @@
         <v>6-150</v>
       </c>
       <c r="M37" t="str">
-        <v/>
+        <v>80</v>
       </c>
       <c r="N37" t="str">
         <v>55</v>
@@ -2883,9 +3315,21 @@
         <v>标准杯</v>
       </c>
       <c r="R37" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S37" t="str">
+        <v/>
+      </c>
+      <c r="T37" t="str">
+        <v>PC</v>
+      </c>
+      <c r="U37" t="str">
+        <v/>
+      </c>
+      <c r="V37" t="str">
+        <v/>
+      </c>
+      <c r="W37" t="str">
         <v/>
       </c>
     </row>
@@ -2918,7 +3362,7 @@
         <v>10</v>
       </c>
       <c r="J38" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K38" t="str">
         <v>0.8-200</v>
@@ -2927,7 +3371,7 @@
         <v>6-150</v>
       </c>
       <c r="M38" t="str">
-        <v/>
+        <v>77</v>
       </c>
       <c r="N38" t="str">
         <v>55</v>
@@ -2942,9 +3386,21 @@
         <v>浅杯 (S)</v>
       </c>
       <c r="R38" t="str">
-        <v>标准速比</v>
+        <v>中速比</v>
       </c>
       <c r="S38" t="str">
+        <v/>
+      </c>
+      <c r="T38" t="str">
+        <v>LT</v>
+      </c>
+      <c r="U38" t="str">
+        <v/>
+      </c>
+      <c r="V38" t="str">
+        <v/>
+      </c>
+      <c r="W38" t="str">
         <v/>
       </c>
     </row>
@@ -2977,7 +3433,7 @@
         <v>10</v>
       </c>
       <c r="J39" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K39" t="str">
         <v>1-200</v>
@@ -2986,7 +3442,7 @@
         <v>8-150</v>
       </c>
       <c r="M39" t="str">
-        <v/>
+        <v>85</v>
       </c>
       <c r="N39" t="str">
         <v>55</v>
@@ -3001,9 +3457,21 @@
         <v>标准杯</v>
       </c>
       <c r="R39" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S39" t="str">
+        <v/>
+      </c>
+      <c r="T39" t="str">
+        <v>LT</v>
+      </c>
+      <c r="U39" t="str">
+        <v/>
+      </c>
+      <c r="V39" t="str">
+        <v/>
+      </c>
+      <c r="W39" t="str">
         <v/>
       </c>
     </row>
@@ -3036,7 +3504,7 @@
         <v>10</v>
       </c>
       <c r="J40" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K40" t="str">
         <v>1-200</v>
@@ -3045,7 +3513,7 @@
         <v>8-150</v>
       </c>
       <c r="M40" t="str">
-        <v/>
+        <v>77</v>
       </c>
       <c r="N40" t="str">
         <v>60</v>
@@ -3060,9 +3528,21 @@
         <v>标准杯</v>
       </c>
       <c r="R40" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>中速比</v>
       </c>
       <c r="S40" t="str">
+        <v/>
+      </c>
+      <c r="T40" t="str">
+        <v>PC</v>
+      </c>
+      <c r="U40" t="str">
+        <v/>
+      </c>
+      <c r="V40" t="str">
+        <v/>
+      </c>
+      <c r="W40" t="str">
         <v/>
       </c>
     </row>
@@ -3095,7 +3575,7 @@
         <v>10</v>
       </c>
       <c r="J41" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K41" t="str">
         <v>1-200</v>
@@ -3104,7 +3584,7 @@
         <v>8-150</v>
       </c>
       <c r="M41" t="str">
-        <v/>
+        <v>93</v>
       </c>
       <c r="N41" t="str">
         <v>60</v>
@@ -3119,9 +3599,21 @@
         <v>标准杯</v>
       </c>
       <c r="R41" t="str">
-        <v>超高速比 (XH/XG)</v>
+        <v>超高速比 (XH)</v>
       </c>
       <c r="S41" t="str">
+        <v/>
+      </c>
+      <c r="T41" t="str">
+        <v>PC</v>
+      </c>
+      <c r="U41" t="str">
+        <v/>
+      </c>
+      <c r="V41" t="str">
+        <v/>
+      </c>
+      <c r="W41" t="str">
         <v/>
       </c>
     </row>
@@ -3154,7 +3646,7 @@
         <v>10</v>
       </c>
       <c r="J42" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K42" t="str">
         <v>1.5-200</v>
@@ -3163,7 +3655,7 @@
         <v>12-150</v>
       </c>
       <c r="M42" t="str">
-        <v/>
+        <v>82</v>
       </c>
       <c r="N42" t="str">
         <v>60</v>
@@ -3178,9 +3670,21 @@
         <v>标准杯</v>
       </c>
       <c r="R42" t="str">
-        <v>标准速比</v>
+        <v>中速比</v>
       </c>
       <c r="S42" t="str">
+        <v/>
+      </c>
+      <c r="T42" t="str">
+        <v>LT</v>
+      </c>
+      <c r="U42" t="str">
+        <v/>
+      </c>
+      <c r="V42" t="str">
+        <v/>
+      </c>
+      <c r="W42" t="str">
         <v/>
       </c>
     </row>
@@ -3213,7 +3717,7 @@
         <v>10</v>
       </c>
       <c r="J43" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K43" t="str">
         <v>1.5-200</v>
@@ -3222,7 +3726,7 @@
         <v>12-150</v>
       </c>
       <c r="M43" t="str">
-        <v/>
+        <v>99</v>
       </c>
       <c r="N43" t="str">
         <v>60</v>
@@ -3237,9 +3741,21 @@
         <v>标准杯</v>
       </c>
       <c r="R43" t="str">
-        <v>超高速比 (XH/XG)</v>
+        <v>超高速比 (XH)</v>
       </c>
       <c r="S43" t="str">
+        <v/>
+      </c>
+      <c r="T43" t="str">
+        <v>LT</v>
+      </c>
+      <c r="U43" t="str">
+        <v/>
+      </c>
+      <c r="V43" t="str">
+        <v/>
+      </c>
+      <c r="W43" t="str">
         <v/>
       </c>
     </row>
@@ -3272,7 +3788,7 @@
         <v>10</v>
       </c>
       <c r="J44" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K44" t="str">
         <v>2-300</v>
@@ -3281,7 +3797,7 @@
         <v>20-150</v>
       </c>
       <c r="M44" t="str">
-        <v/>
+        <v>87</v>
       </c>
       <c r="N44" t="str">
         <v>60</v>
@@ -3296,9 +3812,21 @@
         <v>标准杯</v>
       </c>
       <c r="R44" t="str">
-        <v>标准速比</v>
+        <v>中速比</v>
       </c>
       <c r="S44" t="str">
+        <v/>
+      </c>
+      <c r="T44" t="str">
+        <v>LT</v>
+      </c>
+      <c r="U44" t="str">
+        <v/>
+      </c>
+      <c r="V44" t="str">
+        <v>是</v>
+      </c>
+      <c r="W44" t="str">
         <v/>
       </c>
     </row>
@@ -3331,7 +3859,7 @@
         <v>10</v>
       </c>
       <c r="J45" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K45" t="str">
         <v>2-300</v>
@@ -3340,7 +3868,7 @@
         <v>20-150</v>
       </c>
       <c r="M45" t="str">
-        <v/>
+        <v>105</v>
       </c>
       <c r="N45" t="str">
         <v>60</v>
@@ -3355,9 +3883,21 @@
         <v>标准杯</v>
       </c>
       <c r="R45" t="str">
-        <v>超高速比 (XH/XG)</v>
+        <v>超高速比 (XH)</v>
       </c>
       <c r="S45" t="str">
+        <v/>
+      </c>
+      <c r="T45" t="str">
+        <v>LT</v>
+      </c>
+      <c r="U45" t="str">
+        <v/>
+      </c>
+      <c r="V45" t="str">
+        <v>是</v>
+      </c>
+      <c r="W45" t="str">
         <v/>
       </c>
     </row>
@@ -3390,7 +3930,7 @@
         <v>3</v>
       </c>
       <c r="J46" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K46" t="str">
         <v>0.3-200</v>
@@ -3399,7 +3939,7 @@
         <v>2.5-100</v>
       </c>
       <c r="M46" t="str">
-        <v/>
+        <v>57</v>
       </c>
       <c r="N46" t="str">
         <v>35</v>
@@ -3414,9 +3954,21 @@
         <v>浅杯 (S)</v>
       </c>
       <c r="R46" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S46" t="str">
+        <v/>
+      </c>
+      <c r="T46" t="str">
+        <v>SF</v>
+      </c>
+      <c r="U46" t="str">
+        <v/>
+      </c>
+      <c r="V46" t="str">
+        <v/>
+      </c>
+      <c r="W46" t="str">
         <v/>
       </c>
     </row>
@@ -3449,7 +4001,7 @@
         <v>3</v>
       </c>
       <c r="J47" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K47" t="str">
         <v>0.3-200</v>
@@ -3458,7 +4010,7 @@
         <v>2.5-100</v>
       </c>
       <c r="M47" t="str">
-        <v/>
+        <v>60</v>
       </c>
       <c r="N47" t="str">
         <v>40</v>
@@ -3470,12 +4022,24 @@
         <v>102,000</v>
       </c>
       <c r="Q47" t="str">
-        <v>极浅杯 (SS)</v>
+        <v>超浅杯 (SS)</v>
       </c>
       <c r="R47" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S47" t="str">
+        <v/>
+      </c>
+      <c r="T47" t="str">
+        <v>SF</v>
+      </c>
+      <c r="U47" t="str">
+        <v/>
+      </c>
+      <c r="V47" t="str">
+        <v/>
+      </c>
+      <c r="W47" t="str">
         <v/>
       </c>
     </row>
@@ -3508,7 +4072,7 @@
         <v>3</v>
       </c>
       <c r="J48" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K48" t="str">
         <v>0.3-200</v>
@@ -3517,7 +4081,7 @@
         <v>2.5-100</v>
       </c>
       <c r="M48" t="str">
-        <v/>
+        <v>74</v>
       </c>
       <c r="N48" t="str">
         <v>45</v>
@@ -3529,12 +4093,24 @@
         <v>102,000</v>
       </c>
       <c r="Q48" t="str">
-        <v>极浅杯 (SS)</v>
+        <v>超浅杯 (SS)</v>
       </c>
       <c r="R48" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S48" t="str">
+        <v/>
+      </c>
+      <c r="T48" t="str">
+        <v>SF</v>
+      </c>
+      <c r="U48" t="str">
+        <v/>
+      </c>
+      <c r="V48" t="str">
+        <v/>
+      </c>
+      <c r="W48" t="str">
         <v/>
       </c>
     </row>
@@ -3567,7 +4143,7 @@
         <v>3</v>
       </c>
       <c r="J49" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K49" t="str">
         <v>0.4-200</v>
@@ -3576,7 +4152,7 @@
         <v>3-150</v>
       </c>
       <c r="M49" t="str">
-        <v/>
+        <v>70</v>
       </c>
       <c r="N49" t="str">
         <v>45</v>
@@ -3588,12 +4164,24 @@
         <v>103,000</v>
       </c>
       <c r="Q49" t="str">
-        <v>极浅杯 (SS)</v>
+        <v>超浅杯 (SS)</v>
       </c>
       <c r="R49" t="str">
-        <v>标准速比</v>
+        <v>中速比</v>
       </c>
       <c r="S49" t="str">
+        <v/>
+      </c>
+      <c r="T49" t="str">
+        <v>SF</v>
+      </c>
+      <c r="U49" t="str">
+        <v/>
+      </c>
+      <c r="V49" t="str">
+        <v/>
+      </c>
+      <c r="W49" t="str">
         <v/>
       </c>
     </row>
@@ -3626,7 +4214,7 @@
         <v>3</v>
       </c>
       <c r="J50" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K50" t="str">
         <v>0.4-200</v>
@@ -3635,7 +4223,7 @@
         <v>3-150</v>
       </c>
       <c r="M50" t="str">
-        <v/>
+        <v>80</v>
       </c>
       <c r="N50" t="str">
         <v>45</v>
@@ -3647,12 +4235,24 @@
         <v>103,000</v>
       </c>
       <c r="Q50" t="str">
-        <v>极浅杯 (SS)</v>
+        <v>超浅杯 (SS)</v>
       </c>
       <c r="R50" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S50" t="str">
+        <v/>
+      </c>
+      <c r="T50" t="str">
+        <v>SF</v>
+      </c>
+      <c r="U50" t="str">
+        <v/>
+      </c>
+      <c r="V50" t="str">
+        <v/>
+      </c>
+      <c r="W50" t="str">
         <v/>
       </c>
     </row>
@@ -3685,7 +4285,7 @@
         <v>25</v>
       </c>
       <c r="J51" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K51" t="str">
         <v>3-460_4-300</v>
@@ -3694,7 +4294,7 @@
         <v/>
       </c>
       <c r="M51" t="str">
-        <v/>
+        <v>94</v>
       </c>
       <c r="N51" t="str">
         <v>80</v>
@@ -3709,9 +4309,21 @@
         <v>标准杯</v>
       </c>
       <c r="R51" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S51" t="str">
+        <v/>
+      </c>
+      <c r="T51" t="str">
+        <v/>
+      </c>
+      <c r="U51" t="str">
+        <v/>
+      </c>
+      <c r="V51" t="str">
+        <v/>
+      </c>
+      <c r="W51" t="str">
         <v/>
       </c>
     </row>
@@ -3744,7 +4356,7 @@
         <v>25</v>
       </c>
       <c r="J52" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K52" t="str">
         <v>3-460_4-300</v>
@@ -3753,7 +4365,7 @@
         <v/>
       </c>
       <c r="M52" t="str">
-        <v/>
+        <v>110</v>
       </c>
       <c r="N52" t="str">
         <v>80</v>
@@ -3768,9 +4380,21 @@
         <v>标准杯</v>
       </c>
       <c r="R52" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S52" t="str">
+        <v/>
+      </c>
+      <c r="T52" t="str">
+        <v/>
+      </c>
+      <c r="U52" t="str">
+        <v/>
+      </c>
+      <c r="V52" t="str">
+        <v/>
+      </c>
+      <c r="W52" t="str">
         <v/>
       </c>
     </row>
@@ -3803,7 +4427,7 @@
         <v>25</v>
       </c>
       <c r="J53" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K53" t="str">
         <v>4-380_5-300</v>
@@ -3812,7 +4436,7 @@
         <v/>
       </c>
       <c r="M53" t="str">
-        <v/>
+        <v>99</v>
       </c>
       <c r="N53" t="str">
         <v>85</v>
@@ -3827,9 +4451,21 @@
         <v>标准杯</v>
       </c>
       <c r="R53" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S53" t="str">
+        <v/>
+      </c>
+      <c r="T53" t="str">
+        <v/>
+      </c>
+      <c r="U53" t="str">
+        <v/>
+      </c>
+      <c r="V53" t="str">
+        <v/>
+      </c>
+      <c r="W53" t="str">
         <v/>
       </c>
     </row>
@@ -3862,7 +4498,7 @@
         <v>25</v>
       </c>
       <c r="J54" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K54" t="str">
         <v>4-380_5-300</v>
@@ -3871,7 +4507,7 @@
         <v/>
       </c>
       <c r="M54" t="str">
-        <v/>
+        <v>117</v>
       </c>
       <c r="N54" t="str">
         <v>85</v>
@@ -3886,9 +4522,21 @@
         <v>标准杯</v>
       </c>
       <c r="R54" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S54" t="str">
+        <v/>
+      </c>
+      <c r="T54" t="str">
+        <v/>
+      </c>
+      <c r="U54" t="str">
+        <v/>
+      </c>
+      <c r="V54" t="str">
+        <v/>
+      </c>
+      <c r="W54" t="str">
         <v/>
       </c>
     </row>
@@ -3921,7 +4569,7 @@
         <v>25</v>
       </c>
       <c r="J55" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K55" t="str">
         <v>5-340_6-300</v>
@@ -3930,7 +4578,7 @@
         <v/>
       </c>
       <c r="M55" t="str">
-        <v/>
+        <v>102</v>
       </c>
       <c r="N55" t="str">
         <v>85</v>
@@ -3945,9 +4593,21 @@
         <v>标准杯</v>
       </c>
       <c r="R55" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S55" t="str">
+        <v/>
+      </c>
+      <c r="T55" t="str">
+        <v/>
+      </c>
+      <c r="U55" t="str">
+        <v/>
+      </c>
+      <c r="V55" t="str">
+        <v/>
+      </c>
+      <c r="W55" t="str">
         <v/>
       </c>
     </row>
@@ -3980,7 +4640,7 @@
         <v>25</v>
       </c>
       <c r="J56" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K56" t="str">
         <v>5-340_6-300</v>
@@ -3989,7 +4649,7 @@
         <v/>
       </c>
       <c r="M56" t="str">
-        <v/>
+        <v>133</v>
       </c>
       <c r="N56" t="str">
         <v>85</v>
@@ -4004,9 +4664,21 @@
         <v>标准杯</v>
       </c>
       <c r="R56" t="str">
-        <v>超高速比 (XH/XG)</v>
+        <v>超高速比 (XH)</v>
       </c>
       <c r="S56" t="str">
+        <v/>
+      </c>
+      <c r="T56" t="str">
+        <v/>
+      </c>
+      <c r="U56" t="str">
+        <v/>
+      </c>
+      <c r="V56" t="str">
+        <v/>
+      </c>
+      <c r="W56" t="str">
         <v/>
       </c>
     </row>
@@ -4039,7 +4711,7 @@
         <v>30</v>
       </c>
       <c r="J57" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K57" t="str">
         <v>6-420_8-300</v>
@@ -4048,7 +4720,7 @@
         <v/>
       </c>
       <c r="M57" t="str">
-        <v/>
+        <v>129</v>
       </c>
       <c r="N57" t="str">
         <v>90</v>
@@ -4063,9 +4735,21 @@
         <v>标准杯</v>
       </c>
       <c r="R57" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S57" t="str">
+        <v/>
+      </c>
+      <c r="T57" t="str">
+        <v/>
+      </c>
+      <c r="U57" t="str">
+        <v/>
+      </c>
+      <c r="V57" t="str">
+        <v/>
+      </c>
+      <c r="W57" t="str">
         <v/>
       </c>
     </row>
@@ -4098,7 +4782,7 @@
         <v>30</v>
       </c>
       <c r="J58" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K58" t="str">
         <v>8-370_10-300</v>
@@ -4107,7 +4791,7 @@
         <v/>
       </c>
       <c r="M58" t="str">
-        <v/>
+        <v>111</v>
       </c>
       <c r="N58" t="str">
         <v>90</v>
@@ -4122,9 +4806,21 @@
         <v>标准杯</v>
       </c>
       <c r="R58" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>低速比 (P)</v>
       </c>
       <c r="S58" t="str">
+        <v/>
+      </c>
+      <c r="T58" t="str">
+        <v/>
+      </c>
+      <c r="U58" t="str">
+        <v/>
+      </c>
+      <c r="V58" t="str">
+        <v/>
+      </c>
+      <c r="W58" t="str">
         <v/>
       </c>
     </row>
@@ -4157,7 +4853,7 @@
         <v>30</v>
       </c>
       <c r="J59" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K59" t="str">
         <v>8-370_10-300</v>
@@ -4166,7 +4862,7 @@
         <v/>
       </c>
       <c r="M59" t="str">
-        <v/>
+        <v>138</v>
       </c>
       <c r="N59" t="str">
         <v>90</v>
@@ -4181,9 +4877,21 @@
         <v>标准杯</v>
       </c>
       <c r="R59" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>高速比 (H)</v>
       </c>
       <c r="S59" t="str">
+        <v/>
+      </c>
+      <c r="T59" t="str">
+        <v/>
+      </c>
+      <c r="U59" t="str">
+        <v/>
+      </c>
+      <c r="V59" t="str">
+        <v/>
+      </c>
+      <c r="W59" t="str">
         <v/>
       </c>
     </row>
@@ -4216,7 +4924,7 @@
         <v/>
       </c>
       <c r="J60" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K60" t="str">
         <v>0.3-300_0.5-250</v>
@@ -4225,7 +4933,7 @@
         <v/>
       </c>
       <c r="M60" t="str">
-        <v/>
+        <v>88</v>
       </c>
       <c r="N60" t="str">
         <v>85</v>
@@ -4240,9 +4948,21 @@
         <v>标准杯</v>
       </c>
       <c r="R60" t="str">
-        <v>高速比 (H/HG)</v>
+        <v>中速比</v>
       </c>
       <c r="S60" t="str">
+        <v/>
+      </c>
+      <c r="T60" t="str">
+        <v/>
+      </c>
+      <c r="U60" t="str">
+        <v/>
+      </c>
+      <c r="V60" t="str">
+        <v/>
+      </c>
+      <c r="W60" t="str">
         <v/>
       </c>
     </row>
@@ -4275,7 +4995,7 @@
         <v/>
       </c>
       <c r="J61" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K61" t="str">
         <v>0.6-250_0.8-200</v>
@@ -4284,7 +5004,7 @@
         <v/>
       </c>
       <c r="M61" t="str">
-        <v/>
+        <v>79</v>
       </c>
       <c r="N61" t="str">
         <v>85</v>
@@ -4299,9 +5019,21 @@
         <v>标准杯</v>
       </c>
       <c r="R61" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>中速比</v>
       </c>
       <c r="S61" t="str">
+        <v/>
+      </c>
+      <c r="T61" t="str">
+        <v/>
+      </c>
+      <c r="U61" t="str">
+        <v/>
+      </c>
+      <c r="V61" t="str">
+        <v/>
+      </c>
+      <c r="W61" t="str">
         <v/>
       </c>
     </row>
@@ -4334,7 +5066,7 @@
         <v/>
       </c>
       <c r="J62" t="str">
-        <v/>
+        <v>有</v>
       </c>
       <c r="K62" t="str">
         <v>0.6-250_0.8-200</v>
@@ -4343,7 +5075,7 @@
         <v/>
       </c>
       <c r="M62" t="str">
-        <v/>
+        <v>68</v>
       </c>
       <c r="N62" t="str">
         <v>85</v>
@@ -4358,15 +5090,27 @@
         <v>标准杯</v>
       </c>
       <c r="R62" t="str">
-        <v>低速比 (P/PG)</v>
+        <v>中速比</v>
       </c>
       <c r="S62" t="str">
+        <v/>
+      </c>
+      <c r="T62" t="str">
+        <v/>
+      </c>
+      <c r="U62" t="str">
+        <v/>
+      </c>
+      <c r="V62" t="str">
+        <v/>
+      </c>
+      <c r="W62" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:W62"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/pkgGear/data_raw/daiwa_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_reels_import.xlsx
@@ -476,10 +476,10 @@
         <v>images/daiwa_reels/ソルティガ_main.jpg</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -527,10 +527,10 @@
         <v>images/daiwa_reels/ソルティガ_4000_5000_6000_main.jpg</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -576,10 +576,10 @@
         <v>images/daiwa_reels/EXIST_main.jpg</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -626,10 +626,10 @@
         <v>images/daiwa_reels/セルテート_SW_8000___10000___14000___18000___20000_main.jpg</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -676,10 +676,10 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -848,10 +848,10 @@
         <v/>
       </c>
       <c r="S2" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T2" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U2" t="str">
         <v>有</v>
@@ -934,10 +934,10 @@
         <v/>
       </c>
       <c r="S3" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T3" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U3" t="str">
         <v>有</v>
@@ -1020,10 +1020,10 @@
         <v/>
       </c>
       <c r="S4" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T4" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U4" t="str">
         <v>有</v>
@@ -1106,10 +1106,10 @@
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T5" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U5" t="str">
         <v>有</v>
@@ -1192,10 +1192,10 @@
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T6" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U6" t="str">
         <v>有</v>
@@ -1278,10 +1278,10 @@
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T7" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U7" t="str">
         <v>有</v>
@@ -1364,10 +1364,10 @@
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T8" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U8" t="str">
         <v>有</v>
@@ -1450,10 +1450,10 @@
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T9" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U9" t="str">
         <v>有</v>
@@ -1536,10 +1536,10 @@
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T10" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U10" t="str">
         <v>有</v>
@@ -1622,10 +1622,10 @@
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T11" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U11" t="str">
         <v>有</v>
@@ -1708,10 +1708,10 @@
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T12" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U12" t="str">
         <v>有</v>
@@ -1794,10 +1794,10 @@
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T13" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U13" t="str">
         <v>有</v>
@@ -1880,10 +1880,10 @@
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T14" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U14" t="str">
         <v>有</v>
@@ -1966,10 +1966,10 @@
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T15" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U15" t="str">
         <v>有</v>
@@ -2052,10 +2052,10 @@
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T16" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U16" t="str">
         <v>有</v>
@@ -2138,10 +2138,10 @@
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T17" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U17" t="str">
         <v>有</v>
@@ -2224,10 +2224,10 @@
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T18" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U18" t="str">
         <v>有</v>
@@ -2310,10 +2310,10 @@
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T19" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U19" t="str">
         <v>有</v>
@@ -2396,10 +2396,10 @@
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T20" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U20" t="str">
         <v>有</v>
@@ -2482,10 +2482,10 @@
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T21" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U21" t="str">
         <v>有</v>
@@ -2568,10 +2568,10 @@
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T22" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U22" t="str">
         <v>有</v>
@@ -2654,10 +2654,10 @@
         <v/>
       </c>
       <c r="S23" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T23" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U23" t="str">
         <v>有</v>
@@ -2740,10 +2740,10 @@
         <v/>
       </c>
       <c r="S24" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T24" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U24" t="str">
         <v>有</v>
@@ -2826,10 +2826,10 @@
         <v/>
       </c>
       <c r="S25" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T25" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U25" t="str">
         <v>有</v>
@@ -2912,10 +2912,10 @@
         <v/>
       </c>
       <c r="S26" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T26" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U26" t="str">
         <v>有</v>
@@ -2998,10 +2998,10 @@
         <v/>
       </c>
       <c r="S27" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T27" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U27" t="str">
         <v>有</v>
@@ -3084,10 +3084,10 @@
         <v/>
       </c>
       <c r="S28" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T28" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U28" t="str">
         <v>有</v>
@@ -3170,10 +3170,10 @@
         <v/>
       </c>
       <c r="S29" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T29" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U29" t="str">
         <v>有</v>
@@ -3256,10 +3256,10 @@
         <v/>
       </c>
       <c r="S30" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T30" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U30" t="str">
         <v>有</v>
@@ -3274,7 +3274,7 @@
         <v/>
       </c>
       <c r="Y30" t="str">
-        <v>LT</v>
+        <v/>
       </c>
       <c r="Z30" t="str">
         <v/>
@@ -3342,10 +3342,10 @@
         <v/>
       </c>
       <c r="S31" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T31" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U31" t="str">
         <v>有</v>
@@ -3360,7 +3360,7 @@
         <v/>
       </c>
       <c r="Y31" t="str">
-        <v>LT</v>
+        <v/>
       </c>
       <c r="Z31" t="str">
         <v/>
@@ -3428,10 +3428,10 @@
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T32" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U32" t="str">
         <v>有</v>
@@ -3446,7 +3446,7 @@
         <v/>
       </c>
       <c r="Y32" t="str">
-        <v>LT</v>
+        <v/>
       </c>
       <c r="Z32" t="str">
         <v/>
@@ -3514,10 +3514,10 @@
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T33" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U33" t="str">
         <v>有</v>
@@ -3532,7 +3532,7 @@
         <v/>
       </c>
       <c r="Y33" t="str">
-        <v>LT</v>
+        <v/>
       </c>
       <c r="Z33" t="str">
         <v/>
@@ -3600,10 +3600,10 @@
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T34" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U34" t="str">
         <v>有</v>
@@ -3618,7 +3618,7 @@
         <v/>
       </c>
       <c r="Y34" t="str">
-        <v>LT</v>
+        <v/>
       </c>
       <c r="Z34" t="str">
         <v/>
@@ -3686,10 +3686,10 @@
         <v/>
       </c>
       <c r="S35" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T35" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U35" t="str">
         <v>有</v>
@@ -3704,7 +3704,7 @@
         <v/>
       </c>
       <c r="Y35" t="str">
-        <v>LT</v>
+        <v/>
       </c>
       <c r="Z35" t="str">
         <v/>
@@ -3772,10 +3772,10 @@
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T36" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U36" t="str">
         <v>有</v>
@@ -3858,10 +3858,10 @@
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T37" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U37" t="str">
         <v>有</v>
@@ -3944,10 +3944,10 @@
         <v/>
       </c>
       <c r="S38" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T38" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U38" t="str">
         <v>有</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="Y38" t="str">
-        <v>LT</v>
+        <v/>
       </c>
       <c r="Z38" t="str">
         <v/>
@@ -4030,10 +4030,10 @@
         <v/>
       </c>
       <c r="S39" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T39" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U39" t="str">
         <v>有</v>
@@ -4048,7 +4048,7 @@
         <v/>
       </c>
       <c r="Y39" t="str">
-        <v>LT</v>
+        <v/>
       </c>
       <c r="Z39" t="str">
         <v/>
@@ -4116,10 +4116,10 @@
         <v/>
       </c>
       <c r="S40" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T40" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U40" t="str">
         <v>有</v>
@@ -4202,10 +4202,10 @@
         <v/>
       </c>
       <c r="S41" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T41" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U41" t="str">
         <v>有</v>
@@ -4288,10 +4288,10 @@
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T42" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U42" t="str">
         <v>有</v>
@@ -4306,7 +4306,7 @@
         <v/>
       </c>
       <c r="Y42" t="str">
-        <v>LT</v>
+        <v/>
       </c>
       <c r="Z42" t="str">
         <v/>
@@ -4374,10 +4374,10 @@
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T43" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U43" t="str">
         <v>有</v>
@@ -4392,7 +4392,7 @@
         <v/>
       </c>
       <c r="Y43" t="str">
-        <v>LT</v>
+        <v/>
       </c>
       <c r="Z43" t="str">
         <v/>
@@ -4460,10 +4460,10 @@
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T44" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U44" t="str">
         <v>有</v>
@@ -4478,7 +4478,7 @@
         <v/>
       </c>
       <c r="Y44" t="str">
-        <v>LT</v>
+        <v/>
       </c>
       <c r="Z44" t="str">
         <v/>
@@ -4546,10 +4546,10 @@
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T45" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U45" t="str">
         <v>有</v>
@@ -4564,7 +4564,7 @@
         <v/>
       </c>
       <c r="Y45" t="str">
-        <v>LT</v>
+        <v/>
       </c>
       <c r="Z45" t="str">
         <v/>
@@ -4632,10 +4632,10 @@
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T46" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U46" t="str">
         <v>有</v>
@@ -4718,10 +4718,10 @@
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T47" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U47" t="str">
         <v>有</v>
@@ -4804,10 +4804,10 @@
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T48" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U48" t="str">
         <v>有</v>
@@ -4890,10 +4890,10 @@
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T49" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U49" t="str">
         <v>有</v>
@@ -4976,10 +4976,10 @@
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T50" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U50" t="str">
         <v>有</v>
@@ -5062,10 +5062,10 @@
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T51" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U51" t="str">
         <v>有</v>
@@ -5148,10 +5148,10 @@
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T52" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U52" t="str">
         <v>有</v>
@@ -5234,10 +5234,10 @@
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T53" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U53" t="str">
         <v>有</v>
@@ -5320,10 +5320,10 @@
         <v/>
       </c>
       <c r="S54" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T54" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U54" t="str">
         <v>有</v>
@@ -5406,10 +5406,10 @@
         <v/>
       </c>
       <c r="S55" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T55" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U55" t="str">
         <v>有</v>
@@ -5492,10 +5492,10 @@
         <v/>
       </c>
       <c r="S56" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T56" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U56" t="str">
         <v>有</v>
@@ -5578,10 +5578,10 @@
         <v/>
       </c>
       <c r="S57" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T57" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U57" t="str">
         <v>有</v>
@@ -5664,10 +5664,10 @@
         <v/>
       </c>
       <c r="S58" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T58" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U58" t="str">
         <v>有</v>
@@ -5750,10 +5750,10 @@
         <v/>
       </c>
       <c r="S59" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T59" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U59" t="str">
         <v>有</v>
@@ -5836,10 +5836,10 @@
         <v/>
       </c>
       <c r="S60" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T60" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U60" t="str">
         <v>有</v>
@@ -5922,10 +5922,10 @@
         <v/>
       </c>
       <c r="S61" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T61" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U61" t="str">
         <v>有</v>
@@ -6008,10 +6008,10 @@
         <v/>
       </c>
       <c r="S62" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="T62" t="str">
-        <v>2026-04-04 01:55:53</v>
+        <v>2026-04-04 20:08:17</v>
       </c>
       <c r="U62" t="str">
         <v>有</v>

--- a/GearSage-client/pkgGear/data_raw/daiwa_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_reels_import.xlsx
@@ -473,7 +473,7 @@
         <v>spinning</v>
       </c>
       <c r="I2" t="str">
-        <v>images/daiwa_reels/ソルティガ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC_4000_5000_6000_main.jpg</v>
       </c>
       <c r="J2" t="str">
         <v>2026-04-05T14:36:58.671126Z</v>
@@ -524,7 +524,7 @@
         <v>spinning</v>
       </c>
       <c r="I3" t="str">
-        <v>images/daiwa_reels/ソルティガ_4000_5000_6000_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC_4000_5000_6000_main.jpg</v>
       </c>
       <c r="J3" t="str">
         <v>2026-04-05T14:37:04.963194Z</v>
@@ -573,7 +573,7 @@
         <v>spinning</v>
       </c>
       <c r="I4" t="str">
-        <v>images/daiwa_reels/EXIST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/EXIST_main.jpg</v>
       </c>
       <c r="J4" t="str">
         <v>2026-04-05T14:37:11.658942Z</v>
@@ -623,7 +623,7 @@
         <v>spinning</v>
       </c>
       <c r="I5" t="str">
-        <v>images/daiwa_reels/セルテート_SW_8000___10000___14000___18000___20000_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BB%E3%83%AB%E3%83%86%E3%83%BC%E3%83%88_SW_4000_5000_6000_main.jpg</v>
       </c>
       <c r="J5" t="str">
         <v>2026-04-05T14:37:13.603365Z</v>
@@ -721,7 +721,7 @@
         <v>spinning</v>
       </c>
       <c r="I7" t="str">
-        <v>images/daiwa_reels/セルテート_HD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BB%E3%83%AB%E3%83%86%E3%83%BC%E3%83%88_HD_main.jpg</v>
       </c>
       <c r="J7" t="str">
         <v>2026-04-05T14:37:21.734163Z</v>
@@ -771,7 +771,7 @@
         <v>spinning</v>
       </c>
       <c r="I8" t="str">
-        <v>images/daiwa_reels/セルテート_SW_4000_5000_6000_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BB%E3%83%AB%E3%83%86%E3%83%BC%E3%83%88_SW_4000_5000_6000_main.jpg</v>
       </c>
       <c r="J8" t="str">
         <v>2026-04-05T14:37:28.669103Z</v>
@@ -873,7 +873,7 @@
         <v>spinning</v>
       </c>
       <c r="I10" t="str">
-        <v>images/daiwa_reels/エアリティ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%A8%E3%82%A2%E3%83%AA%E3%83%86%E3%82%A3_ST_main.jpg</v>
       </c>
       <c r="J10" t="str">
         <v>2026-04-05T14:37:40.618600Z</v>
@@ -923,7 +923,7 @@
         <v>spinning</v>
       </c>
       <c r="I11" t="str">
-        <v>images/daiwa_reels/エアリティ_ST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%A8%E3%82%A2%E3%83%AA%E3%83%86%E3%82%A3_ST_main.jpg</v>
       </c>
       <c r="J11" t="str">
         <v>2026-04-05T14:37:46.839914Z</v>
@@ -973,7 +973,7 @@
         <v>spinning</v>
       </c>
       <c r="I12" t="str">
-        <v>images/daiwa_reels/セルテート_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BB%E3%83%AB%E3%83%86%E3%83%BC%E3%83%88_HD_main.jpg</v>
       </c>
       <c r="J12" t="str">
         <v>2026-04-05T14:37:47.828581Z</v>
@@ -1023,7 +1023,7 @@
         <v>spinning</v>
       </c>
       <c r="I13" t="str">
-        <v>images/daiwa_reels/エメラルダス_AIR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%A8%E3%83%A1%E3%83%A9%E3%83%AB%E3%83%80%E3%82%B9_AIR_main.jpg</v>
       </c>
       <c r="J13" t="str">
         <v>2026-04-05T14:37:50.096730Z</v>
@@ -1073,7 +1073,7 @@
         <v>spinning</v>
       </c>
       <c r="I14" t="str">
-        <v>images/daiwa_reels/ルビアス_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%83%AB%E3%83%93%E3%82%A2%E3%82%B9_ST_main.jpg</v>
       </c>
       <c r="J14" t="str">
         <v>2026-04-05T14:37:57.793850Z</v>
@@ -1221,7 +1221,7 @@
         <v>spinning</v>
       </c>
       <c r="I17" t="str">
-        <v>images/daiwa_reels/ルビアス_ST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%83%AB%E3%83%93%E3%82%A2%E3%82%B9_ST_main.jpg</v>
       </c>
       <c r="J17" t="str">
         <v>2026-04-05T14:38:07.769091Z</v>
@@ -1370,7 +1370,7 @@
         <v>spinning</v>
       </c>
       <c r="I20" t="str">
-        <v>images/daiwa_reels/エメラルダス_RX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%A8%E3%83%A1%E3%83%A9%E3%83%AB%E3%83%80%E3%82%B9_RX_main.jpg</v>
       </c>
       <c r="J20" t="str">
         <v>2026-04-05T14:38:12.642500Z</v>
@@ -1468,7 +1468,7 @@
         <v>spinning</v>
       </c>
       <c r="I22" t="str">
-        <v>images/daiwa_reels/カルディア_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%AB%E3%83%AB%E3%83%87%E3%82%A3%E3%82%A2_main.jpg</v>
       </c>
       <c r="J22" t="str">
         <v>2026-04-05T14:38:25.700195Z</v>
@@ -1616,7 +1616,7 @@
         <v>spinning</v>
       </c>
       <c r="I25" t="str">
-        <v>images/daiwa_reels/月下美人_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA_BF_TW_PE_SP_main.jpg</v>
       </c>
       <c r="J25" t="str">
         <v>2026-04-05T14:38:34.700529Z</v>
@@ -1665,7 +1665,7 @@
         <v>spinning</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9_BF_TW_main.jpg</v>
       </c>
       <c r="J26" t="str">
         <v>2026-04-05T14:38:40.792539Z</v>
@@ -1813,7 +1813,7 @@
         <v>spinning</v>
       </c>
       <c r="I29" t="str">
-        <v>images/daiwa_reels/レグザ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%83%AC%E3%82%B0%E3%82%B6_main.jpg</v>
       </c>
       <c r="J29" t="str">
         <v>2026-04-05T14:38:58.278242Z</v>
@@ -1912,7 +1912,7 @@
         <v>spinning</v>
       </c>
       <c r="I31" t="str">
-        <v>images/daiwa_reels/フリームス_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%83%95%E3%83%AA%E3%83%BC%E3%83%A0%E3%82%B9_main.jpg</v>
       </c>
       <c r="J31" t="str">
         <v>2026-04-05T14:39:04.561638Z</v>
@@ -2011,7 +2011,7 @@
         <v>spinning</v>
       </c>
       <c r="I33" t="str">
-        <v>images/daiwa_reels/イプリミ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%A4%E3%83%97%E3%83%AA%E3%83%9F_main.jpg</v>
       </c>
       <c r="J33" t="str">
         <v>2026-04-05T14:39:18.443898Z</v>
@@ -2062,7 +2062,7 @@
         <v>spinning</v>
       </c>
       <c r="I34" t="str">
-        <v>images/daiwa_reels/エメラルダス_X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%A8%E3%83%A1%E3%83%A9%E3%83%AB%E3%83%80%E3%82%B9_X_main.jpg</v>
       </c>
       <c r="J34" t="str">
         <v>2026-04-05T14:39:24.533666Z</v>
@@ -2161,7 +2161,7 @@
         <v>spinning</v>
       </c>
       <c r="I36" t="str">
-        <v>images/daiwa_reels/アオリマチックBR_LT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%A2%E3%82%AA%E3%83%AA%E3%83%9E%E3%83%81%E3%83%83%E3%82%AFBR_LT_main.jpg</v>
       </c>
       <c r="J36" t="str">
         <v>2026-04-05T14:39:33.655150Z</v>
@@ -2211,7 +2211,7 @@
         <v>spinning</v>
       </c>
       <c r="I37" t="str">
-        <v>images/daiwa_reels/月下美人_X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA_X_main.jpg</v>
       </c>
       <c r="J37" t="str">
         <v>2026-04-05T14:39:35.787707Z</v>
@@ -2260,7 +2260,7 @@
         <v>spinning</v>
       </c>
       <c r="I38" t="str">
-        <v>images/daiwa_reels/レガリス_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%83%AC%E3%82%AC%E3%83%AA%E3%82%B9_main.jpg</v>
       </c>
       <c r="J38" t="str">
         <v>2026-04-05T14:39:42.740714Z</v>
@@ -2360,7 +2360,7 @@
         <v>spinning</v>
       </c>
       <c r="I40" t="str">
-        <v>images/daiwa_reels/レブロス_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%83%AC%E3%83%96%E3%83%AD%E3%82%B9_main.jpg</v>
       </c>
       <c r="J40" t="str">
         <v>2026-04-05T14:39:55.715342Z</v>
